--- a/backend/templates/hybrid/hermetik_hybrid.xlsx
+++ b/backend/templates/hybrid/hermetik_hybrid.xlsx
@@ -5106,89 +5106,6 @@
   </twoCellAnchor>
   <twoCellAnchor editAs="oneCell">
     <from>
-      <col>6</col>
-      <colOff>28574</colOff>
-      <row>52</row>
-      <rowOff>28575</rowOff>
-    </from>
-    <to>
-      <col>11</col>
-      <colOff>1444</colOff>
-      <row>55</row>
-      <rowOff>19050</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Resim 11"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r="62" b="55405"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3038474" y="9344025"/>
-          <a:ext cx="2316020" cy="561975"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>11</col>
-      <colOff>38100</colOff>
-      <row>52</row>
-      <rowOff>123825</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>549564</colOff>
-      <row>54</row>
-      <rowOff>177827</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Resim 12"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5391150" y="9439275"/>
-          <a:ext cx="1121064" cy="435003"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
       <col>10</col>
       <colOff>0</colOff>
       <row>1</row>
@@ -5208,7 +5125,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -5249,7 +5166,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" b="4827"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -5291,7 +5208,7 @@
         </cNvPicPr>
       </nvPicPr>
       <blipFill rotWithShape="1">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" b="8860"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
@@ -5301,48 +5218,6 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5969870" y="207754"/>
           <a:ext cx="581977" cy="432093"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>31</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>6</col>
-      <colOff>420896</colOff>
-      <row>50</row>
-      <rowOff>134327</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Resim 2"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="37248" t="22100" r="38025" b="30578"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="0" y="5238750"/>
-          <a:ext cx="3437146" cy="3700096"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -5401,88 +5276,6 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>10</col>
-      <colOff>219075</colOff>
-      <row>74</row>
-      <rowOff>19050</rowOff>
-    </from>
-    <to>
-      <col>14</col>
-      <colOff>66675</colOff>
-      <row>77</row>
-      <rowOff>132739</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Resim 5"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3324225" y="9448800"/>
-          <a:ext cx="1181100" cy="628039"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>14</col>
-      <colOff>190500</colOff>
-      <row>74</row>
-      <rowOff>142875</rowOff>
-    </from>
-    <to>
-      <col>18</col>
-      <colOff>135675</colOff>
-      <row>77</row>
-      <rowOff>107320</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Resim 4"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4635500" y="8112125"/>
-          <a:ext cx="1278675" cy="488320"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -5519,88 +5312,6 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="238125" y="190500"/>
           <a:ext cx="1819275" cy="745435"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>123824</colOff>
-      <row>40</row>
-      <rowOff>66675</rowOff>
-    </from>
-    <to>
-      <col>13</col>
-      <colOff>109053</colOff>
-      <row>42</row>
-      <rowOff>257175</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Resim 8"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3257549" y="9344025"/>
-          <a:ext cx="1433029" cy="762000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>12</col>
-      <colOff>349250</colOff>
-      <row>40</row>
-      <rowOff>174625</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>215050</colOff>
-      <row>42</row>
-      <rowOff>91445</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Resim 5"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4603750" y="7524750"/>
-          <a:ext cx="1278675" cy="488320"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -5659,88 +5370,6 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>104775</colOff>
-      <row>50</row>
-      <rowOff>28575</rowOff>
-    </from>
-    <to>
-      <col>13</col>
-      <colOff>90004</colOff>
-      <row>52</row>
-      <rowOff>219075</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Resim 5"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3238500" y="9315450"/>
-          <a:ext cx="1433029" cy="762000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>50</row>
-      <rowOff>219075</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>192825</colOff>
-      <row>52</row>
-      <rowOff>135895</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Resim 4"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4581525" y="9505950"/>
-          <a:ext cx="1278675" cy="488320"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -5777,88 +5406,6 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="235324" y="190500"/>
           <a:ext cx="1819275" cy="745435"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>257736</colOff>
-      <row>48</row>
-      <rowOff>67236</rowOff>
-    </from>
-    <to>
-      <col>13</col>
-      <colOff>256412</colOff>
-      <row>50</row>
-      <rowOff>246530</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Resim 8"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3361765" y="9379324"/>
-          <a:ext cx="1433029" cy="762000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>13</col>
-      <colOff>22413</colOff>
-      <row>48</row>
-      <rowOff>201706</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>225323</colOff>
-      <row>50</row>
-      <rowOff>107320</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Resim 6"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4560795" y="9513794"/>
-          <a:ext cx="1278675" cy="488320"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -5917,88 +5464,6 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>266700</colOff>
-      <row>44</row>
-      <rowOff>57150</rowOff>
-    </from>
-    <to>
-      <col>13</col>
-      <colOff>251929</colOff>
-      <row>46</row>
-      <rowOff>247650</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Resim 6"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3400425" y="8848725"/>
-          <a:ext cx="1433029" cy="762000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>13</col>
-      <colOff>133350</colOff>
-      <row>44</row>
-      <rowOff>219075</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>326175</colOff>
-      <row>46</row>
-      <rowOff>135895</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Resim 4"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4714875" y="9010650"/>
-          <a:ext cx="1278675" cy="488320"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -6035,88 +5500,6 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="238125" y="190500"/>
           <a:ext cx="1819275" cy="745435"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>285750</colOff>
-      <row>44</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <to>
-      <col>13</col>
-      <colOff>270979</colOff>
-      <row>46</row>
-      <rowOff>238125</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Resim 7"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3419475" y="9363075"/>
-          <a:ext cx="1433029" cy="762000"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>13</col>
-      <colOff>32288</colOff>
-      <row>44</row>
-      <rowOff>226018</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>245455</colOff>
-      <row>46</row>
-      <rowOff>133151</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Resim 5"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4536483" y="9621865"/>
-          <a:ext cx="1278675" cy="488320"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -6175,89 +5558,6 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>47624</colOff>
-      <row>52</row>
-      <rowOff>66674</rowOff>
-    </from>
-    <to>
-      <col>15</col>
-      <colOff>154195</colOff>
-      <row>54</row>
-      <rowOff>57149</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Resim 5"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r="4040" b="56470"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3133724" y="9248774"/>
-          <a:ext cx="2278271" cy="561975"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>14</col>
-      <colOff>114300</colOff>
-      <row>52</row>
-      <rowOff>247650</rowOff>
-    </from>
-    <to>
-      <col>17</col>
-      <colOff>82839</colOff>
-      <row>54</row>
-      <rowOff>111153</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Resim 6"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5010150" y="9429750"/>
-          <a:ext cx="1121064" cy="435003"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -6294,89 +5594,6 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="107674" y="66261"/>
           <a:ext cx="2017125" cy="745435"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>10</col>
-      <colOff>81308</colOff>
-      <row>78</row>
-      <rowOff>46463</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>234322</colOff>
-      <row>80</row>
-      <rowOff>162621</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Resim 6"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r="-1725" b="54025"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3217588" y="9257835"/>
-          <a:ext cx="2174173" cy="534329"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>15</col>
-      <colOff>209086</colOff>
-      <row>79</row>
-      <rowOff>11617</rowOff>
-    </from>
-    <to>
-      <col>18</col>
-      <colOff>319570</colOff>
-      <row>81</row>
-      <rowOff>28449</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Resim 3"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5029665" y="9432074"/>
-          <a:ext cx="1121064" cy="435003"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -6462,89 +5679,6 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>28574</colOff>
-      <row>45</row>
-      <rowOff>190499</rowOff>
-    </from>
-    <to>
-      <col>14</col>
-      <colOff>73819</colOff>
-      <row>47</row>
-      <rowOff>104774</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="10" name="Resim 9"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" t="-1" r="2758" b="54343"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3238499" y="9467849"/>
-          <a:ext cx="1902620" cy="485775"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>14</col>
-      <colOff>28575</colOff>
-      <row>45</row>
-      <rowOff>180975</rowOff>
-    </from>
-    <to>
-      <col>17</col>
-      <colOff>35214</colOff>
-      <row>47</row>
-      <rowOff>44478</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Resim 10"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5095875" y="9458325"/>
-          <a:ext cx="1121064" cy="435003"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -6608,89 +5742,6 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="238125" y="190500"/>
           <a:ext cx="1885950" cy="745435"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>57149</colOff>
-      <row>45</row>
-      <rowOff>47625</rowOff>
-    </from>
-    <to>
-      <col>14</col>
-      <colOff>268381</colOff>
-      <row>46</row>
-      <rowOff>257175</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Resim 8"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r="3480" b="57500"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3267074" y="9324975"/>
-          <a:ext cx="2068607" cy="495300"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>14</col>
-      <colOff>47625</colOff>
-      <row>45</row>
-      <rowOff>171450</rowOff>
-    </from>
-    <to>
-      <col>17</col>
-      <colOff>54264</colOff>
-      <row>47</row>
-      <rowOff>34953</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Resim 10"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5114925" y="9448800"/>
-          <a:ext cx="1121064" cy="435003"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -6830,89 +5881,6 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>67234</colOff>
-      <row>50</row>
-      <rowOff>123265</rowOff>
-    </from>
-    <to>
-      <col>14</col>
-      <colOff>67238</colOff>
-      <row>52</row>
-      <rowOff>78441</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Resim 10"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r="5512" b="56559"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3518646" y="10208559"/>
-          <a:ext cx="2151533" cy="537882"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>14</col>
-      <colOff>89648</colOff>
-      <row>50</row>
-      <rowOff>246530</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>392682</colOff>
-      <row>52</row>
-      <rowOff>98827</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Resim 12"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5692589" y="10331824"/>
-          <a:ext cx="1121064" cy="435003"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -6987,89 +5955,6 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>33617</colOff>
-      <row>50</row>
-      <rowOff>212911</rowOff>
-    </from>
-    <to>
-      <col>13</col>
-      <colOff>358589</colOff>
-      <row>52</row>
-      <rowOff>67234</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Resim 7"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill rotWithShape="1">
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" t="1" r="-988" b="57143"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3216088" y="10286999"/>
-          <a:ext cx="1893795" cy="437029"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>13</col>
-      <colOff>369794</colOff>
-      <row>50</row>
-      <rowOff>224118</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>280623</colOff>
-      <row>52</row>
-      <rowOff>76415</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Resim 8"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="5121088" y="10298206"/>
-          <a:ext cx="1121064" cy="435003"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -7106,88 +5991,6 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="235323" y="190500"/>
           <a:ext cx="1748117" cy="745435"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>246529</colOff>
-      <row>47</row>
-      <rowOff>56029</rowOff>
-    </from>
-    <to>
-      <col>13</col>
-      <colOff>171262</colOff>
-      <row>49</row>
-      <rowOff>225798</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Resim 7"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3260911" y="9390529"/>
-          <a:ext cx="1415116" cy="752475"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>13</col>
-      <colOff>156883</colOff>
-      <row>47</row>
-      <rowOff>212912</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>258941</colOff>
-      <row>49</row>
-      <rowOff>118526</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Resim 6"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4661648" y="9547412"/>
-          <a:ext cx="1278675" cy="488320"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -7246,88 +6049,6 @@
     </pic>
     <clientData/>
   </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>56029</colOff>
-      <row>44</row>
-      <rowOff>56029</rowOff>
-    </from>
-    <to>
-      <col>12</col>
-      <colOff>305734</colOff>
-      <row>46</row>
-      <rowOff>225798</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Resim 6"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3238500" y="9468970"/>
-          <a:ext cx="1415116" cy="752475"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>45</row>
-      <rowOff>0</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>68440</colOff>
-      <row>46</row>
-      <rowOff>196967</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Resim 4"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4751294" y="9704294"/>
-          <a:ext cx="1278675" cy="488320"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
 </wsDr>
 </file>
 
@@ -7364,88 +6085,6 @@
         <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="235324" y="190500"/>
           <a:ext cx="1885950" cy="745435"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>9</col>
-      <colOff>179295</colOff>
-      <row>44</row>
-      <rowOff>44824</rowOff>
-    </from>
-    <to>
-      <col>13</col>
-      <colOff>25588</colOff>
-      <row>46</row>
-      <rowOff>214593</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Resim 7"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="3361766" y="9502589"/>
-          <a:ext cx="1415116" cy="752475"/>
-        </a:xfrm>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
-          <avLst/>
-        </a:prstGeom>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
-      </spPr>
-    </pic>
-    <clientData/>
-  </twoCellAnchor>
-  <twoCellAnchor editAs="oneCell">
-    <from>
-      <col>13</col>
-      <colOff>89647</colOff>
-      <row>44</row>
-      <rowOff>201706</rowOff>
-    </from>
-    <to>
-      <col>16</col>
-      <colOff>158087</colOff>
-      <row>46</row>
-      <rowOff>107320</rowOff>
-    </to>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Resim 4"/>
-        <cNvPicPr>
-          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
-        </cNvPicPr>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:off x="4840941" y="9659471"/>
-          <a:ext cx="1278675" cy="488320"/>
         </a:xfrm>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
@@ -8456,7 +7095,7 @@
       <c r="S10" s="41" t="n"/>
       <c r="T10" s="11" t="n"/>
     </row>
-    <row r="11">
+    <row r="11" ht="15" customHeight="1" s="227">
       <c r="A11" s="10" t="n"/>
       <c r="B11" s="280" t="inlineStr">
         <is>
@@ -8468,11 +7107,7 @@
           <t>:</t>
         </is>
       </c>
-      <c r="G11" s="278" t="inlineStr">
-        <is>
-          <t>ULUSOY</t>
-        </is>
-      </c>
+      <c r="G11" s="278" t="n"/>
       <c r="H11" s="486" t="n"/>
       <c r="I11" s="486" t="n"/>
       <c r="J11" s="486" t="n"/>
@@ -8486,11 +7121,7 @@
           <t xml:space="preserve">: </t>
         </is>
       </c>
-      <c r="O11" s="556" t="inlineStr">
-        <is>
-          <t>USFB-36R</t>
-        </is>
-      </c>
+      <c r="O11" s="556" t="n"/>
       <c r="P11" s="486" t="n"/>
       <c r="Q11" s="486" t="n"/>
       <c r="R11" s="486" t="n"/>
@@ -8519,7 +7150,7 @@
       <c r="S12" s="143" t="n"/>
       <c r="T12" s="11" t="n"/>
     </row>
-    <row r="13">
+    <row r="13" ht="15" customHeight="1" s="227">
       <c r="A13" s="10" t="n"/>
       <c r="B13" s="247" t="inlineStr">
         <is>
@@ -8531,9 +7162,7 @@
           <t>:</t>
         </is>
       </c>
-      <c r="G13" s="284" t="n">
-        <v>630</v>
-      </c>
+      <c r="G13" s="284" t="n"/>
       <c r="H13" s="486" t="n"/>
       <c r="I13" s="486" t="n"/>
       <c r="J13" s="486" t="n"/>
@@ -8547,11 +7176,7 @@
           <t>:</t>
         </is>
       </c>
-      <c r="O13" s="279" t="inlineStr">
-        <is>
-          <t>2016</t>
-        </is>
-      </c>
+      <c r="O13" s="279" t="n"/>
       <c r="P13" s="486" t="n"/>
       <c r="Q13" s="486" t="n"/>
       <c r="R13" s="486" t="n"/>
@@ -8580,7 +7205,7 @@
       <c r="S14" s="143" t="n"/>
       <c r="T14" s="11" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="15" customHeight="1" s="227">
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="280" t="inlineStr">
         <is>
@@ -8592,9 +7217,7 @@
           <t xml:space="preserve">:  </t>
         </is>
       </c>
-      <c r="G15" s="284" t="n">
-        <v>36000</v>
-      </c>
+      <c r="G15" s="284" t="n"/>
       <c r="H15" s="486" t="n"/>
       <c r="I15" s="486" t="n"/>
       <c r="J15" s="486" t="n"/>
@@ -8608,9 +7231,7 @@
           <t>:</t>
         </is>
       </c>
-      <c r="O15" s="283" t="n">
-        <v>2196</v>
-      </c>
+      <c r="O15" s="283" t="n"/>
       <c r="P15" s="486" t="n"/>
       <c r="Q15" s="486" t="n"/>
       <c r="R15" s="486" t="n"/>
@@ -8651,11 +7272,7 @@
           <t>:</t>
         </is>
       </c>
-      <c r="G17" s="284" t="inlineStr">
-        <is>
-          <t>220 Vac</t>
-        </is>
-      </c>
+      <c r="G17" s="284" t="n"/>
       <c r="H17" s="486" t="n"/>
       <c r="I17" s="486" t="n"/>
       <c r="J17" s="486" t="n"/>
@@ -8669,11 +7286,7 @@
           <t>:</t>
         </is>
       </c>
-      <c r="O17" s="283" t="inlineStr">
-        <is>
-          <t>24 Vdc</t>
-        </is>
-      </c>
+      <c r="O17" s="283" t="n"/>
       <c r="P17" s="486" t="n"/>
       <c r="Q17" s="486" t="n"/>
       <c r="R17" s="486" t="n"/>
@@ -8832,7 +7445,7 @@
       <c r="S23" s="143" t="n"/>
       <c r="T23" s="11" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15" customHeight="1" s="227">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="280" t="inlineStr">
         <is>
@@ -8844,17 +7457,9 @@
           <t>:</t>
         </is>
       </c>
-      <c r="G24" s="306" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
-        </is>
-      </c>
+      <c r="G24" s="306" t="n"/>
       <c r="H24" s="487" t="n"/>
-      <c r="I24" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="I24" s="93" t="n"/>
       <c r="J24" s="559" t="n"/>
       <c r="K24" s="291" t="inlineStr">
         <is>
@@ -8866,17 +7471,9 @@
           <t>:</t>
         </is>
       </c>
-      <c r="P24" s="306" t="inlineStr">
-        <is>
-          <t>YAPILDI</t>
-        </is>
-      </c>
+      <c r="P24" s="306" t="n"/>
       <c r="Q24" s="487" t="n"/>
-      <c r="R24" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="R24" s="93" t="n"/>
       <c r="S24" s="559" t="n"/>
       <c r="T24" s="11" t="n"/>
     </row>
@@ -8902,7 +7499,7 @@
       <c r="S25" s="120" t="n"/>
       <c r="T25" s="11" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15" customHeight="1" s="227">
       <c r="A26" s="10" t="n"/>
       <c r="B26" s="280" t="inlineStr">
         <is>
@@ -8914,19 +7511,9 @@
           <t>:</t>
         </is>
       </c>
-      <c r="G26" s="89" t="n">
-        <v>24</v>
-      </c>
-      <c r="H26" s="306" t="inlineStr">
-        <is>
-          <t>Vdc</t>
-        </is>
-      </c>
-      <c r="I26" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="G26" s="89" t="n"/>
+      <c r="H26" s="306" t="n"/>
+      <c r="I26" s="93" t="n"/>
       <c r="J26" s="559" t="n"/>
       <c r="K26" s="291" t="inlineStr">
         <is>
@@ -8938,17 +7525,9 @@
           <t>:</t>
         </is>
       </c>
-      <c r="P26" s="306" t="inlineStr">
-        <is>
-          <t>YAPILDI</t>
-        </is>
-      </c>
+      <c r="P26" s="306" t="n"/>
       <c r="Q26" s="487" t="n"/>
-      <c r="R26" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="R26" s="93" t="n"/>
       <c r="S26" s="559" t="n"/>
       <c r="T26" s="11" t="n"/>
     </row>
@@ -8974,7 +7553,7 @@
       <c r="S27" s="120" t="n"/>
       <c r="T27" s="11" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15" customHeight="1" s="227">
       <c r="A28" s="10" t="n"/>
       <c r="B28" s="280" t="inlineStr">
         <is>
@@ -8986,17 +7565,9 @@
           <t>:</t>
         </is>
       </c>
-      <c r="G28" s="306" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
-        </is>
-      </c>
+      <c r="G28" s="306" t="n"/>
       <c r="H28" s="487" t="n"/>
-      <c r="I28" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="I28" s="93" t="n"/>
       <c r="J28" s="93" t="n"/>
       <c r="K28" s="291" t="inlineStr">
         <is>
@@ -9008,17 +7579,9 @@
           <t xml:space="preserve">: </t>
         </is>
       </c>
-      <c r="P28" s="306" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
-        </is>
-      </c>
+      <c r="P28" s="306" t="n"/>
       <c r="Q28" s="487" t="n"/>
-      <c r="R28" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="R28" s="93" t="n"/>
       <c r="S28" s="93" t="n"/>
       <c r="T28" s="11" t="n"/>
     </row>
@@ -9044,7 +7607,7 @@
       <c r="S29" s="120" t="n"/>
       <c r="T29" s="11" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15" customHeight="1" s="227">
       <c r="A30" s="10" t="n"/>
       <c r="B30" s="280" t="inlineStr">
         <is>
@@ -9056,17 +7619,9 @@
           <t>:</t>
         </is>
       </c>
-      <c r="G30" s="306" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
-        </is>
-      </c>
+      <c r="G30" s="306" t="n"/>
       <c r="H30" s="487" t="n"/>
-      <c r="I30" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="I30" s="93" t="n"/>
       <c r="J30" s="93" t="n"/>
       <c r="K30" s="291" t="inlineStr">
         <is>
@@ -9078,17 +7633,9 @@
           <t>:</t>
         </is>
       </c>
-      <c r="P30" s="306" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
-        </is>
-      </c>
+      <c r="P30" s="306" t="n"/>
       <c r="Q30" s="487" t="n"/>
-      <c r="R30" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="R30" s="93" t="n"/>
       <c r="S30" s="93" t="n"/>
       <c r="T30" s="11" t="n"/>
     </row>
@@ -9114,7 +7661,7 @@
       <c r="S31" s="120" t="n"/>
       <c r="T31" s="11" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15" customHeight="1" s="227">
       <c r="A32" s="10" t="n"/>
       <c r="B32" s="280" t="inlineStr">
         <is>
@@ -9126,17 +7673,9 @@
           <t>:</t>
         </is>
       </c>
-      <c r="G32" s="306" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
-        </is>
-      </c>
+      <c r="G32" s="306" t="n"/>
       <c r="H32" s="487" t="n"/>
-      <c r="I32" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="I32" s="93" t="n"/>
       <c r="J32" s="93" t="n"/>
       <c r="K32" s="291" t="inlineStr">
         <is>
@@ -9148,17 +7687,9 @@
           <t>:</t>
         </is>
       </c>
-      <c r="P32" s="306" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
-        </is>
-      </c>
+      <c r="P32" s="306" t="n"/>
       <c r="Q32" s="487" t="n"/>
-      <c r="R32" s="93" t="inlineStr">
-        <is>
-          <t>ü</t>
-        </is>
-      </c>
+      <c r="R32" s="93" t="n"/>
       <c r="S32" s="93" t="n"/>
       <c r="T32" s="11" t="n"/>
     </row>
@@ -9399,45 +7930,35 @@
           <t>L-1</t>
         </is>
       </c>
-      <c r="C39" s="527" t="n">
-        <v>2000</v>
-      </c>
+      <c r="C39" s="527" t="n"/>
       <c r="D39" s="99" t="n"/>
       <c r="E39" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="F39" s="527" t="n">
-        <v>4000</v>
-      </c>
+      <c r="F39" s="527" t="n"/>
       <c r="G39" s="99" t="n"/>
       <c r="H39" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="I39" s="527" t="n">
-        <v>6000</v>
-      </c>
+      <c r="I39" s="527" t="n"/>
       <c r="J39" s="99" t="n"/>
       <c r="K39" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="L39" s="527" t="n">
-        <v>8000</v>
-      </c>
+      <c r="L39" s="527" t="n"/>
       <c r="M39" s="99" t="n"/>
       <c r="N39" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="O39" s="527" t="n">
-        <v>10000</v>
-      </c>
+      <c r="O39" s="527" t="n"/>
       <c r="P39" s="99" t="n"/>
       <c r="Q39" s="563" t="inlineStr">
         <is>
@@ -9518,45 +8039,35 @@
           <t>L-2</t>
         </is>
       </c>
-      <c r="C41" s="527" t="n">
-        <v>2000</v>
-      </c>
+      <c r="C41" s="527" t="n"/>
       <c r="D41" s="99" t="n"/>
       <c r="E41" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="F41" s="527" t="n">
-        <v>4000</v>
-      </c>
+      <c r="F41" s="527" t="n"/>
       <c r="G41" s="99" t="n"/>
       <c r="H41" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="I41" s="527" t="n">
-        <v>6000</v>
-      </c>
+      <c r="I41" s="527" t="n"/>
       <c r="J41" s="99" t="n"/>
       <c r="K41" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="L41" s="527" t="n">
-        <v>8000</v>
-      </c>
+      <c r="L41" s="527" t="n"/>
       <c r="M41" s="99" t="n"/>
       <c r="N41" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="O41" s="527" t="n">
-        <v>10000</v>
-      </c>
+      <c r="O41" s="527" t="n"/>
       <c r="P41" s="99" t="n"/>
       <c r="Q41" s="563" t="inlineStr">
         <is>
@@ -9637,45 +8148,35 @@
           <t>L-3</t>
         </is>
       </c>
-      <c r="C43" s="527" t="n">
-        <v>2000</v>
-      </c>
+      <c r="C43" s="527" t="n"/>
       <c r="D43" s="99" t="n"/>
       <c r="E43" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="F43" s="527" t="n">
-        <v>4000</v>
-      </c>
+      <c r="F43" s="527" t="n"/>
       <c r="G43" s="99" t="n"/>
       <c r="H43" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="I43" s="527" t="n">
-        <v>6000</v>
-      </c>
+      <c r="I43" s="527" t="n"/>
       <c r="J43" s="99" t="n"/>
       <c r="K43" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="L43" s="527" t="n">
-        <v>8000</v>
-      </c>
+      <c r="L43" s="527" t="n"/>
       <c r="M43" s="99" t="n"/>
       <c r="N43" s="563" t="inlineStr">
         <is>
           <t>GΩ</t>
         </is>
       </c>
-      <c r="O43" s="527" t="n">
-        <v>10000</v>
-      </c>
+      <c r="O43" s="527" t="n"/>
       <c r="P43" s="99" t="n"/>
       <c r="Q43" s="563" t="inlineStr">
         <is>
@@ -9984,11 +8485,7 @@
           <t>L-1</t>
         </is>
       </c>
-      <c r="C50" s="565" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
+      <c r="C50" s="565" t="n"/>
       <c r="D50" s="99" t="n"/>
       <c r="E50" s="99" t="n"/>
       <c r="F50" s="566" t="inlineStr">
@@ -9996,9 +8493,7 @@
           <t>kV</t>
         </is>
       </c>
-      <c r="G50" s="567" t="n">
-        <v>20000</v>
-      </c>
+      <c r="G50" s="567" t="n"/>
       <c r="H50" s="99" t="n"/>
       <c r="I50" s="563" t="inlineStr">
         <is>
@@ -10009,17 +8504,11 @@
         <f>IF(G50&gt;50,1,0)</f>
         <v/>
       </c>
-      <c r="K50" s="376" t="inlineStr">
-        <is>
-          <t>80.00A</t>
-        </is>
-      </c>
+      <c r="K50" s="376" t="n"/>
       <c r="L50" s="99" t="n"/>
       <c r="M50" s="99" t="n"/>
       <c r="N50" s="482" t="n"/>
-      <c r="O50" s="569" t="n">
-        <v>38</v>
-      </c>
+      <c r="O50" s="569" t="n"/>
       <c r="P50" s="99" t="n"/>
       <c r="Q50" s="99" t="n"/>
       <c r="R50" s="563" t="inlineStr">
@@ -10100,11 +8589,7 @@
           <t>L-2</t>
         </is>
       </c>
-      <c r="C52" s="565" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
+      <c r="C52" s="565" t="n"/>
       <c r="D52" s="99" t="n"/>
       <c r="E52" s="99" t="n"/>
       <c r="F52" s="566" t="inlineStr">
@@ -10112,9 +8597,7 @@
           <t>kV</t>
         </is>
       </c>
-      <c r="G52" s="567" t="n">
-        <v>20000</v>
-      </c>
+      <c r="G52" s="567" t="n"/>
       <c r="H52" s="99" t="n"/>
       <c r="I52" s="563" t="inlineStr">
         <is>
@@ -10125,17 +8608,11 @@
         <f>IF(G52&gt;50,1,0)</f>
         <v/>
       </c>
-      <c r="K52" s="376" t="inlineStr">
-        <is>
-          <t>80.00A</t>
-        </is>
-      </c>
+      <c r="K52" s="376" t="n"/>
       <c r="L52" s="99" t="n"/>
       <c r="M52" s="99" t="n"/>
       <c r="N52" s="482" t="n"/>
-      <c r="O52" s="574" t="n">
-        <v>40</v>
-      </c>
+      <c r="O52" s="574" t="n"/>
       <c r="P52" s="99" t="n"/>
       <c r="Q52" s="99" t="n"/>
       <c r="R52" s="563" t="inlineStr">
@@ -10216,11 +8693,7 @@
           <t>L-3</t>
         </is>
       </c>
-      <c r="C54" s="565" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
+      <c r="C54" s="565" t="n"/>
       <c r="D54" s="99" t="n"/>
       <c r="E54" s="99" t="n"/>
       <c r="F54" s="566" t="inlineStr">
@@ -10228,9 +8701,7 @@
           <t>kV</t>
         </is>
       </c>
-      <c r="G54" s="567" t="n">
-        <v>20000</v>
-      </c>
+      <c r="G54" s="567" t="n"/>
       <c r="H54" s="99" t="n"/>
       <c r="I54" s="563" t="inlineStr">
         <is>
@@ -10241,17 +8712,11 @@
         <f>IF(G54&gt;50,1,0)</f>
         <v/>
       </c>
-      <c r="K54" s="376" t="inlineStr">
-        <is>
-          <t>80.00A</t>
-        </is>
-      </c>
+      <c r="K54" s="376" t="n"/>
       <c r="L54" s="99" t="n"/>
       <c r="M54" s="99" t="n"/>
       <c r="N54" s="482" t="n"/>
-      <c r="O54" s="574" t="n">
-        <v>54</v>
-      </c>
+      <c r="O54" s="574" t="n"/>
       <c r="P54" s="99" t="n"/>
       <c r="Q54" s="99" t="n"/>
       <c r="R54" s="563" t="inlineStr">
@@ -10545,9 +9010,7 @@
           <t>L-1</t>
         </is>
       </c>
-      <c r="C61" s="575" t="n">
-        <v>52.63</v>
-      </c>
+      <c r="C61" s="575" t="n"/>
       <c r="D61" s="99" t="n"/>
       <c r="E61" s="482" t="inlineStr">
         <is>
@@ -10565,9 +9028,7 @@
         </is>
       </c>
       <c r="I61" s="482" t="n"/>
-      <c r="J61" s="575" t="n">
-        <v>69.03</v>
-      </c>
+      <c r="J61" s="575" t="n"/>
       <c r="K61" s="99" t="n"/>
       <c r="L61" s="482" t="inlineStr">
         <is>
@@ -10585,11 +9046,7 @@
         </is>
       </c>
       <c r="P61" s="482" t="n"/>
-      <c r="Q61" s="576" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
-        </is>
-      </c>
+      <c r="Q61" s="576" t="n"/>
       <c r="R61" s="99" t="n"/>
       <c r="S61" s="482" t="n"/>
       <c r="T61" s="11" t="n"/>
@@ -10657,9 +9114,7 @@
           <t>L-2</t>
         </is>
       </c>
-      <c r="C63" s="575" t="n">
-        <v>54.14</v>
-      </c>
+      <c r="C63" s="575" t="n"/>
       <c r="D63" s="99" t="n"/>
       <c r="E63" s="482" t="inlineStr">
         <is>
@@ -10674,9 +9129,7 @@
       <c r="G63" s="99" t="n"/>
       <c r="H63" s="99" t="n"/>
       <c r="I63" s="482" t="n"/>
-      <c r="J63" s="575" t="n">
-        <v>66.56999999999999</v>
-      </c>
+      <c r="J63" s="575" t="n"/>
       <c r="K63" s="99" t="n"/>
       <c r="L63" s="482" t="inlineStr">
         <is>
@@ -10691,11 +9144,7 @@
       <c r="N63" s="99" t="n"/>
       <c r="O63" s="99" t="n"/>
       <c r="P63" s="482" t="n"/>
-      <c r="Q63" s="576" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
-        </is>
-      </c>
+      <c r="Q63" s="576" t="n"/>
       <c r="R63" s="99" t="n"/>
       <c r="S63" s="482" t="n"/>
       <c r="T63" s="11" t="n"/>
@@ -10737,25 +9186,21 @@
       <c r="S64" s="212" t="n"/>
       <c r="T64" s="11" t="n"/>
     </row>
-    <row r="65">
+    <row r="65" ht="15" customHeight="1" s="227">
       <c r="A65" s="10" t="n"/>
       <c r="B65" s="504" t="inlineStr">
         <is>
           <t>L-3</t>
         </is>
       </c>
-      <c r="C65" s="575" t="n">
-        <v>50.45</v>
-      </c>
+      <c r="C65" s="575" t="n"/>
       <c r="D65" s="99" t="n"/>
       <c r="E65" s="482" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="F65" s="527" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="F65" s="527" t="n"/>
       <c r="G65" s="99" t="n"/>
       <c r="H65" s="398" t="inlineStr">
         <is>
@@ -10763,18 +9208,14 @@
         </is>
       </c>
       <c r="I65" s="482" t="n"/>
-      <c r="J65" s="575" t="n">
-        <v>68.79000000000001</v>
-      </c>
+      <c r="J65" s="575" t="n"/>
       <c r="K65" s="99" t="n"/>
       <c r="L65" s="482" t="inlineStr">
         <is>
           <t>ms</t>
         </is>
       </c>
-      <c r="M65" s="527" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="M65" s="527" t="n"/>
       <c r="N65" s="99" t="n"/>
       <c r="O65" s="398" t="inlineStr">
         <is>
@@ -10782,11 +9223,7 @@
         </is>
       </c>
       <c r="P65" s="482" t="n"/>
-      <c r="Q65" s="576" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
-        </is>
-      </c>
+      <c r="Q65" s="576" t="n"/>
       <c r="R65" s="99" t="n"/>
       <c r="S65" s="482" t="n"/>
       <c r="T65" s="11" t="n"/>
@@ -11085,9 +9522,7 @@
           <t>:</t>
         </is>
       </c>
-      <c r="F77" s="598" t="n">
-        <v>88258</v>
-      </c>
+      <c r="F77" s="598" t="n"/>
       <c r="J77" s="212" t="n"/>
       <c r="K77" s="267" t="n"/>
       <c r="L77" s="277" t="n"/>
@@ -11114,11 +9549,7 @@
           <t>:</t>
         </is>
       </c>
-      <c r="F78" s="602" t="inlineStr">
-        <is>
-          <t>K202439698</t>
-        </is>
-      </c>
+      <c r="F78" s="602" t="n"/>
       <c r="G78" s="50" t="n"/>
       <c r="H78" s="50" t="n"/>
       <c r="I78" s="50" t="n"/>
@@ -11156,7 +9587,7 @@
       <c r="S79" s="16" t="n"/>
       <c r="T79" s="17" t="n"/>
     </row>
-    <row r="80">
+    <row r="80" ht="15" customHeight="1" s="227">
       <c r="V80" s="604">
         <f>C61-C63</f>
         <v/>
@@ -11166,7 +9597,7 @@
         <v/>
       </c>
     </row>
-    <row r="81">
+    <row r="81" ht="15" customHeight="1" s="227">
       <c r="V81" s="604">
         <f>C61-C65</f>
         <v/>
@@ -11176,7 +9607,7 @@
         <v/>
       </c>
     </row>
-    <row r="82">
+    <row r="82" ht="15" customHeight="1" s="227">
       <c r="V82" s="604">
         <f>C63-C65</f>
         <v/>
@@ -11186,7 +9617,7 @@
         <v/>
       </c>
     </row>
-    <row r="83">
+    <row r="83" ht="15" customHeight="1" s="227">
       <c r="V83" s="604">
         <f>C63-C61</f>
         <v/>
@@ -11196,7 +9627,7 @@
         <v/>
       </c>
     </row>
-    <row r="84">
+    <row r="84" ht="15" customHeight="1" s="227">
       <c r="V84" s="604">
         <f>C65-C61</f>
         <v/>
@@ -11206,7 +9637,7 @@
         <v/>
       </c>
     </row>
-    <row r="85">
+    <row r="85" ht="15" customHeight="1" s="227">
       <c r="V85" s="604">
         <f>C65-C63</f>
         <v/>
@@ -11369,7 +9800,7 @@
     <col width="9.140625" customWidth="1" style="227" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1" s="227">
       <c r="A1" s="12" t="n"/>
       <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
@@ -11582,7 +10013,7 @@
       <c r="Q9" s="143" t="n"/>
       <c r="R9" s="11" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="15" customHeight="1" s="227">
       <c r="A10" s="10" t="n"/>
       <c r="B10" s="421" t="inlineStr">
         <is>
@@ -11590,11 +10021,7 @@
         </is>
       </c>
       <c r="C10" s="482" t="n"/>
-      <c r="D10" s="422" t="inlineStr">
-        <is>
-          <t>Hilmi GÜL</t>
-        </is>
-      </c>
+      <c r="D10" s="422" t="n"/>
       <c r="E10" s="99" t="n"/>
       <c r="F10" s="99" t="n"/>
       <c r="G10" s="482" t="n"/>
@@ -11604,11 +10031,7 @@
         </is>
       </c>
       <c r="I10" s="482" t="n"/>
-      <c r="J10" s="374" t="inlineStr">
-        <is>
-          <t>METREL MI 3210</t>
-        </is>
-      </c>
+      <c r="J10" s="374" t="n"/>
       <c r="K10" s="99" t="n"/>
       <c r="L10" s="482" t="n"/>
       <c r="M10" s="374" t="inlineStr">
@@ -11617,9 +10040,7 @@
         </is>
       </c>
       <c r="N10" s="482" t="n"/>
-      <c r="O10" s="374" t="n">
-        <v>16060016</v>
-      </c>
+      <c r="O10" s="374" t="n"/>
       <c r="P10" s="99" t="n"/>
       <c r="Q10" s="482" t="n"/>
       <c r="R10" s="11" t="n"/>
@@ -11752,7 +10173,7 @@
       <c r="Q15" s="143" t="n"/>
       <c r="R15" s="11" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="15" customHeight="1" s="227">
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="345" t="inlineStr">
         <is>
@@ -11794,7 +10215,7 @@
       <c r="Q16" s="482" t="n"/>
       <c r="R16" s="11" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="15" customHeight="1" s="227">
       <c r="A17" s="10" t="n"/>
       <c r="B17" s="515" t="inlineStr">
         <is>
@@ -11844,7 +10265,7 @@
       <c r="Q17" s="482" t="n"/>
       <c r="R17" s="11" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="15" customHeight="1" s="227">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="515" t="inlineStr">
         <is>
@@ -11894,7 +10315,7 @@
       <c r="Q18" s="482" t="n"/>
       <c r="R18" s="11" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="15" customHeight="1" s="227">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="515" t="inlineStr">
         <is>
@@ -11944,7 +10365,7 @@
       <c r="Q19" s="482" t="n"/>
       <c r="R19" s="11" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="15" customHeight="1" s="227">
       <c r="A20" s="33" t="n"/>
       <c r="Q20" s="211" t="n"/>
       <c r="R20" s="11" t="n"/>
@@ -11953,22 +10374,22 @@
         <v/>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15" customHeight="1" s="227">
       <c r="A21" s="33" t="n"/>
       <c r="Q21" s="212" t="n"/>
       <c r="R21" s="11" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15" customHeight="1" s="227">
       <c r="A22" s="33" t="n"/>
       <c r="Q22" s="212" t="n"/>
       <c r="R22" s="11" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15" customHeight="1" s="227">
       <c r="A23" s="33" t="n"/>
       <c r="Q23" s="212" t="n"/>
       <c r="R23" s="11" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15" customHeight="1" s="227">
       <c r="A24" s="33" t="n"/>
       <c r="Q24" s="212" t="n"/>
       <c r="R24" s="11" t="n"/>
@@ -11977,17 +10398,17 @@
         <v/>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15" customHeight="1" s="227">
       <c r="A25" s="33" t="n"/>
       <c r="Q25" s="212" t="n"/>
       <c r="R25" s="11" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15" customHeight="1" s="227">
       <c r="A26" s="33" t="n"/>
       <c r="Q26" s="212" t="n"/>
       <c r="R26" s="11" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15" customHeight="1" s="227">
       <c r="A27" s="33" t="n"/>
       <c r="Q27" s="212" t="n"/>
       <c r="R27" s="11" t="n"/>
@@ -11997,7 +10418,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15" customHeight="1" s="227">
       <c r="A28" s="33" t="n"/>
       <c r="Q28" s="212" t="n"/>
       <c r="R28" s="11" t="n"/>
@@ -12358,8 +10779,8 @@
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="J40:Q40"/>
-    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="D37:Q38"/>
     <mergeCell ref="K3:Q3"/>
@@ -12422,7 +10843,7 @@
     <col width="9.140625" customWidth="1" style="227" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1" s="227">
       <c r="A1" s="12" t="n"/>
       <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
@@ -12635,7 +11056,7 @@
       <c r="Q9" s="143" t="n"/>
       <c r="R9" s="11" t="n"/>
     </row>
-    <row r="10">
+    <row r="10" ht="15" customHeight="1" s="227">
       <c r="A10" s="10" t="n"/>
       <c r="B10" s="421" t="inlineStr">
         <is>
@@ -12643,11 +11064,7 @@
         </is>
       </c>
       <c r="C10" s="482" t="n"/>
-      <c r="D10" s="422" t="inlineStr">
-        <is>
-          <t>Hilmi GÜL</t>
-        </is>
-      </c>
+      <c r="D10" s="422" t="n"/>
       <c r="E10" s="99" t="n"/>
       <c r="F10" s="99" t="n"/>
       <c r="G10" s="482" t="n"/>
@@ -12657,11 +11074,7 @@
         </is>
       </c>
       <c r="I10" s="482" t="n"/>
-      <c r="J10" s="374" t="inlineStr">
-        <is>
-          <t>STS 5000</t>
-        </is>
-      </c>
+      <c r="J10" s="374" t="n"/>
       <c r="K10" s="99" t="n"/>
       <c r="L10" s="482" t="n"/>
       <c r="M10" s="374" t="inlineStr">
@@ -12670,11 +11083,7 @@
         </is>
       </c>
       <c r="N10" s="482" t="n"/>
-      <c r="O10" s="374" t="inlineStr">
-        <is>
-          <t>19B20</t>
-        </is>
-      </c>
+      <c r="O10" s="374" t="n"/>
       <c r="P10" s="99" t="n"/>
       <c r="Q10" s="482" t="n"/>
       <c r="R10" s="11" t="n"/>
@@ -12794,7 +11203,7 @@
       <c r="Q15" s="41" t="n"/>
       <c r="R15" s="11" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="15" customHeight="1" s="227">
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="384" t="inlineStr">
         <is>
@@ -12811,7 +11220,7 @@
       <c r="Q16" s="212" t="n"/>
       <c r="R16" s="11" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="15" customHeight="1" s="227">
       <c r="A17" s="10" t="n"/>
       <c r="B17" s="377" t="inlineStr">
         <is>
@@ -12843,7 +11252,7 @@
       <c r="Q17" s="212" t="n"/>
       <c r="R17" s="11" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="15" customHeight="1" s="227">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="377" t="n"/>
       <c r="F18" s="446" t="n"/>
@@ -12864,7 +11273,7 @@
       <c r="Q18" s="212" t="n"/>
       <c r="R18" s="11" t="n"/>
     </row>
-    <row r="19">
+    <row r="19" ht="15" customHeight="1" s="227">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="377" t="inlineStr">
         <is>
@@ -12887,7 +11296,7 @@
       <c r="Q19" s="212" t="n"/>
       <c r="R19" s="11" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="15" customHeight="1" s="227">
       <c r="A20" s="10" t="n"/>
       <c r="B20" s="302" t="inlineStr">
         <is>
@@ -12990,7 +11399,7 @@
       <c r="Q23" s="482" t="n"/>
       <c r="R23" s="11" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15" customHeight="1" s="227">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="39" t="n"/>
       <c r="C24" s="40" t="n"/>
@@ -13015,7 +11424,7 @@
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15" customHeight="1" s="227">
       <c r="A25" s="10" t="n"/>
       <c r="B25" s="384" t="inlineStr">
         <is>
@@ -13038,7 +11447,7 @@
         </is>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15" customHeight="1" s="227">
       <c r="A26" s="10" t="n"/>
       <c r="B26" s="377" t="inlineStr">
         <is>
@@ -13075,7 +11484,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="15" customHeight="1" s="227">
       <c r="A27" s="10" t="n"/>
       <c r="B27" s="377" t="n"/>
       <c r="F27" s="446" t="n"/>
@@ -13101,7 +11510,7 @@
         </is>
       </c>
     </row>
-    <row r="28">
+    <row r="28" ht="15" customHeight="1" s="227">
       <c r="A28" s="10" t="n"/>
       <c r="B28" s="377" t="inlineStr">
         <is>
@@ -13129,7 +11538,7 @@
         </is>
       </c>
     </row>
-    <row r="29">
+    <row r="29" ht="15" customHeight="1" s="227">
       <c r="A29" s="10" t="n"/>
       <c r="B29" s="302" t="inlineStr">
         <is>
@@ -13240,7 +11649,7 @@
       <c r="Q32" s="482" t="n"/>
       <c r="R32" s="11" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15" customHeight="1" s="227">
       <c r="A33" s="10" t="n"/>
       <c r="B33" s="39" t="n"/>
       <c r="C33" s="40" t="n"/>
@@ -13260,7 +11669,7 @@
       <c r="Q33" s="41" t="n"/>
       <c r="R33" s="11" t="n"/>
     </row>
-    <row r="34">
+    <row r="34" ht="15" customHeight="1" s="227">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="384" t="inlineStr">
         <is>
@@ -13278,7 +11687,7 @@
       <c r="Q34" s="212" t="n"/>
       <c r="R34" s="11" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15" customHeight="1" s="227">
       <c r="A35" s="10" t="n"/>
       <c r="B35" s="377" t="inlineStr">
         <is>
@@ -13310,7 +11719,7 @@
       <c r="Q35" s="212" t="n"/>
       <c r="R35" s="11" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15" customHeight="1" s="227">
       <c r="A36" s="10" t="n"/>
       <c r="B36" s="377" t="n"/>
       <c r="F36" s="446" t="n"/>
@@ -13738,8 +12147,8 @@
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="F16:I16"/>
     <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B8:I8"/>
     <mergeCell ref="N39:O39"/>
-    <mergeCell ref="B8:I8"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="P39:Q39"/>
     <mergeCell ref="J28:M28"/>
@@ -13875,7 +12284,7 @@
     <col width="9.140625" customWidth="1" style="227" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1" s="227">
       <c r="A1" s="12" t="n"/>
       <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
@@ -14071,7 +12480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15" customHeight="1" s="227">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="421" t="inlineStr">
         <is>
@@ -14092,11 +12501,7 @@
         </is>
       </c>
       <c r="I9" s="482" t="n"/>
-      <c r="J9" s="374" t="inlineStr">
-        <is>
-          <t>METREL MI 3210</t>
-        </is>
-      </c>
+      <c r="J9" s="374" t="n"/>
       <c r="K9" s="99" t="n"/>
       <c r="L9" s="482" t="n"/>
       <c r="M9" s="374" t="inlineStr">
@@ -14105,9 +12510,7 @@
         </is>
       </c>
       <c r="N9" s="482" t="n"/>
-      <c r="O9" s="374" t="n">
-        <v>16060016</v>
-      </c>
+      <c r="O9" s="374" t="n"/>
       <c r="P9" s="99" t="n"/>
       <c r="Q9" s="482" t="n"/>
       <c r="R9" s="11" t="n"/>
@@ -14560,7 +12963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="15" customHeight="1" s="227">
       <c r="A25" s="33" t="n"/>
       <c r="B25" s="398" t="inlineStr">
         <is>
@@ -14628,7 +13031,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="15" customHeight="1" s="227">
       <c r="A26" s="33" t="n"/>
       <c r="B26" s="398" t="inlineStr">
         <is>
@@ -14670,7 +13073,7 @@
       <c r="Q26" s="213" t="n"/>
       <c r="R26" s="11" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15" customHeight="1" s="227">
       <c r="A27" s="33" t="n"/>
       <c r="B27" s="398" t="inlineStr">
         <is>
@@ -14734,7 +13137,7 @@
       </c>
       <c r="R27" s="11" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15" customHeight="1" s="227">
       <c r="A28" s="33" t="n"/>
       <c r="B28" s="626" t="inlineStr">
         <is>
@@ -14853,7 +13256,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15" customHeight="1" s="227">
       <c r="A32" s="10" t="n"/>
       <c r="B32" s="3" t="n"/>
       <c r="C32" s="127" t="n"/>
@@ -14872,7 +13275,7 @@
         </is>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="15" customHeight="1" s="227">
       <c r="A33" s="10" t="n"/>
       <c r="B33" s="3" t="n"/>
       <c r="C33" s="127" t="n"/>
@@ -14891,7 +13294,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
+    <row r="34" ht="15" customHeight="1" s="227">
       <c r="A34" s="10" t="n"/>
       <c r="B34" s="24" t="n"/>
       <c r="C34" s="25" t="n"/>
@@ -14911,7 +13314,7 @@
       <c r="Q34" s="143" t="n"/>
       <c r="R34" s="11" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15" customHeight="1" s="227">
       <c r="A35" s="10" t="n"/>
       <c r="B35" s="3" t="n"/>
       <c r="C35" s="127" t="n"/>
@@ -14931,7 +13334,7 @@
       <c r="Q35" s="143" t="n"/>
       <c r="R35" s="11" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15" customHeight="1" s="227">
       <c r="A36" s="10" t="n"/>
       <c r="B36" s="3" t="n"/>
       <c r="C36" s="127" t="n"/>
@@ -15293,34 +13696,34 @@
       <c r="Q52" s="16" t="n"/>
       <c r="R52" s="17" t="n"/>
     </row>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
+    <row r="53" ht="15" customHeight="1" s="227"/>
+    <row r="54" ht="15" customHeight="1" s="227"/>
+    <row r="55" ht="15" customHeight="1" s="227"/>
     <row r="56" ht="18.75" customHeight="1" s="227">
       <c r="S56" s="54" t="n"/>
     </row>
-    <row r="57">
+    <row r="57" ht="15" customHeight="1" s="227">
       <c r="S57" s="127" t="n"/>
     </row>
-    <row r="58">
+    <row r="58" ht="15" customHeight="1" s="227">
       <c r="S58" s="27" t="n"/>
     </row>
-    <row r="59">
+    <row r="59" ht="15" customHeight="1" s="227">
       <c r="S59" s="127" t="n"/>
     </row>
-    <row r="60">
+    <row r="60" ht="15" customHeight="1" s="227">
       <c r="S60" s="634" t="n"/>
     </row>
-    <row r="61">
+    <row r="61" ht="15" customHeight="1" s="227">
       <c r="S61" s="127" t="n"/>
     </row>
-    <row r="62">
+    <row r="62" ht="15" customHeight="1" s="227">
       <c r="S62" s="127" t="n"/>
     </row>
-    <row r="63">
+    <row r="63" ht="15" customHeight="1" s="227">
       <c r="S63" s="127" t="n"/>
     </row>
-    <row r="64">
+    <row r="64" ht="15" customHeight="1" s="227">
       <c r="S64" s="127" t="n"/>
     </row>
   </sheetData>
@@ -15392,8 +13795,8 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="B28:E28"/>
+    <mergeCell ref="W38:AJ38"/>
     <mergeCell ref="I27:I28"/>
-    <mergeCell ref="W38:AJ38"/>
     <mergeCell ref="J23:Q23"/>
     <mergeCell ref="W28:AD28"/>
     <mergeCell ref="N19:Q19"/>
@@ -15434,7 +13837,7 @@
     <col width="9.140625" customWidth="1" style="227" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1" s="227">
       <c r="A1" s="12" t="n"/>
       <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
@@ -15626,7 +14029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15" customHeight="1" s="227">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="421" t="inlineStr">
         <is>
@@ -15634,11 +14037,7 @@
         </is>
       </c>
       <c r="C9" s="482" t="n"/>
-      <c r="D9" s="422" t="inlineStr">
-        <is>
-          <t>Hilmi GÜL</t>
-        </is>
-      </c>
+      <c r="D9" s="422" t="n"/>
       <c r="E9" s="99" t="n"/>
       <c r="F9" s="99" t="n"/>
       <c r="G9" s="482" t="n"/>
@@ -15648,11 +14047,7 @@
         </is>
       </c>
       <c r="I9" s="482" t="n"/>
-      <c r="J9" s="374" t="inlineStr">
-        <is>
-          <t>METREL MI 3210</t>
-        </is>
-      </c>
+      <c r="J9" s="374" t="n"/>
       <c r="K9" s="99" t="n"/>
       <c r="L9" s="482" t="n"/>
       <c r="M9" s="374" t="inlineStr">
@@ -15661,9 +14056,7 @@
         </is>
       </c>
       <c r="N9" s="482" t="n"/>
-      <c r="O9" s="374" t="n">
-        <v>16060016</v>
-      </c>
+      <c r="O9" s="374" t="n"/>
       <c r="P9" s="99" t="n"/>
       <c r="Q9" s="482" t="n"/>
       <c r="R9" s="11" t="n"/>
@@ -15759,7 +14152,7 @@
       <c r="Q13" s="482" t="n"/>
       <c r="R13" s="11" t="n"/>
     </row>
-    <row r="14">
+    <row r="14" ht="15" customHeight="1" s="227">
       <c r="A14" s="10" t="n"/>
       <c r="B14" s="3" t="n"/>
       <c r="C14" s="127" t="n"/>
@@ -15779,7 +14172,7 @@
       <c r="Q14" s="143" t="n"/>
       <c r="R14" s="11" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="15" customHeight="1" s="227">
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="345" t="n"/>
       <c r="C15" s="99" t="n"/>
@@ -15815,7 +14208,7 @@
       <c r="Q15" s="482" t="n"/>
       <c r="R15" s="11" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="15" customHeight="1" s="227">
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="515" t="inlineStr">
         <is>
@@ -15823,9 +14216,7 @@
         </is>
       </c>
       <c r="C16" s="482" t="n"/>
-      <c r="D16" s="515" t="n">
-        <v>20000</v>
-      </c>
+      <c r="D16" s="515" t="n"/>
       <c r="E16" s="482" t="n"/>
       <c r="F16" s="516" t="inlineStr">
         <is>
@@ -15833,9 +14224,7 @@
         </is>
       </c>
       <c r="G16" s="482" t="n"/>
-      <c r="H16" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H16" s="397" t="n"/>
       <c r="I16" s="99" t="n"/>
       <c r="J16" s="607" t="inlineStr">
         <is>
@@ -15864,7 +14253,7 @@
       <c r="Q16" s="482" t="n"/>
       <c r="R16" s="11" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="15" customHeight="1" s="227">
       <c r="A17" s="10" t="n"/>
       <c r="B17" s="515" t="inlineStr">
         <is>
@@ -15872,9 +14261,7 @@
         </is>
       </c>
       <c r="C17" s="482" t="n"/>
-      <c r="D17" s="515" t="n">
-        <v>20000</v>
-      </c>
+      <c r="D17" s="515" t="n"/>
       <c r="E17" s="482" t="n"/>
       <c r="F17" s="515" t="inlineStr">
         <is>
@@ -15882,9 +14269,7 @@
         </is>
       </c>
       <c r="G17" s="482" t="n"/>
-      <c r="H17" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H17" s="397" t="n"/>
       <c r="I17" s="99" t="n"/>
       <c r="J17" s="607" t="inlineStr">
         <is>
@@ -15918,7 +14303,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15" customHeight="1" s="227">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="515" t="inlineStr">
         <is>
@@ -15926,9 +14311,7 @@
         </is>
       </c>
       <c r="C18" s="482" t="n"/>
-      <c r="D18" s="515" t="n">
-        <v>20000</v>
-      </c>
+      <c r="D18" s="515" t="n"/>
       <c r="E18" s="482" t="n"/>
       <c r="F18" s="515" t="inlineStr">
         <is>
@@ -15936,9 +14319,7 @@
         </is>
       </c>
       <c r="G18" s="482" t="n"/>
-      <c r="H18" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H18" s="397" t="n"/>
       <c r="I18" s="99" t="n"/>
       <c r="J18" s="607" t="inlineStr">
         <is>
@@ -15972,7 +14353,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15" customHeight="1" s="227">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="118" t="n"/>
       <c r="C19" s="52" t="n"/>
@@ -16026,7 +14407,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15" customHeight="1" s="227">
       <c r="A21" s="10" t="n"/>
       <c r="B21" s="3" t="n"/>
       <c r="C21" s="127" t="n"/>
@@ -16051,7 +14432,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15" customHeight="1" s="227">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="345" t="n"/>
       <c r="C22" s="99" t="n"/>
@@ -16092,7 +14473,7 @@
         </is>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="15" customHeight="1" s="227">
       <c r="A23" s="10" t="n"/>
       <c r="B23" s="515" t="inlineStr">
         <is>
@@ -16100,9 +14481,7 @@
         </is>
       </c>
       <c r="C23" s="482" t="n"/>
-      <c r="D23" s="515" t="n">
-        <v>7100</v>
-      </c>
+      <c r="D23" s="515" t="n"/>
       <c r="E23" s="482" t="n"/>
       <c r="F23" s="516" t="inlineStr">
         <is>
@@ -16110,9 +14489,7 @@
         </is>
       </c>
       <c r="G23" s="482" t="n"/>
-      <c r="H23" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H23" s="397" t="n"/>
       <c r="I23" s="99" t="n"/>
       <c r="J23" s="607" t="inlineStr">
         <is>
@@ -16141,7 +14518,7 @@
       <c r="Q23" s="482" t="n"/>
       <c r="R23" s="11" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15" customHeight="1" s="227">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="515" t="inlineStr">
         <is>
@@ -16149,9 +14526,7 @@
         </is>
       </c>
       <c r="C24" s="482" t="n"/>
-      <c r="D24" s="515" t="n">
-        <v>20000</v>
-      </c>
+      <c r="D24" s="515" t="n"/>
       <c r="E24" s="482" t="n"/>
       <c r="F24" s="515" t="inlineStr">
         <is>
@@ -16159,9 +14534,7 @@
         </is>
       </c>
       <c r="G24" s="482" t="n"/>
-      <c r="H24" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H24" s="397" t="n"/>
       <c r="I24" s="99" t="n"/>
       <c r="J24" s="607" t="inlineStr">
         <is>
@@ -16190,7 +14563,7 @@
       <c r="Q24" s="482" t="n"/>
       <c r="R24" s="11" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15" customHeight="1" s="227">
       <c r="A25" s="10" t="n"/>
       <c r="B25" s="515" t="inlineStr">
         <is>
@@ -16198,9 +14571,7 @@
         </is>
       </c>
       <c r="C25" s="482" t="n"/>
-      <c r="D25" s="515" t="n">
-        <v>20000</v>
-      </c>
+      <c r="D25" s="515" t="n"/>
       <c r="E25" s="482" t="n"/>
       <c r="F25" s="515" t="inlineStr">
         <is>
@@ -16208,9 +14579,7 @@
         </is>
       </c>
       <c r="G25" s="482" t="n"/>
-      <c r="H25" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H25" s="397" t="n"/>
       <c r="I25" s="99" t="n"/>
       <c r="J25" s="607" t="inlineStr">
         <is>
@@ -16239,7 +14608,7 @@
       <c r="Q25" s="482" t="n"/>
       <c r="R25" s="11" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15" customHeight="1" s="227">
       <c r="A26" s="10" t="n"/>
       <c r="B26" s="118" t="n"/>
       <c r="C26" s="52" t="n"/>
@@ -16283,7 +14652,7 @@
       <c r="Q27" s="482" t="n"/>
       <c r="R27" s="11" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15" customHeight="1" s="227">
       <c r="A28" s="10" t="n"/>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="127" t="n"/>
@@ -16303,7 +14672,7 @@
       <c r="Q28" s="143" t="n"/>
       <c r="R28" s="11" t="n"/>
     </row>
-    <row r="29">
+    <row r="29" ht="15" customHeight="1" s="227">
       <c r="A29" s="10" t="n"/>
       <c r="B29" s="345" t="inlineStr">
         <is>
@@ -16343,7 +14712,7 @@
       <c r="Q29" s="482" t="n"/>
       <c r="R29" s="11" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15" customHeight="1" s="227">
       <c r="A30" s="10" t="n"/>
       <c r="B30" s="515" t="inlineStr">
         <is>
@@ -16351,9 +14720,7 @@
         </is>
       </c>
       <c r="C30" s="482" t="n"/>
-      <c r="D30" s="515" t="n">
-        <v>22.9</v>
-      </c>
+      <c r="D30" s="515" t="n"/>
       <c r="E30" s="482" t="n"/>
       <c r="F30" s="516" t="inlineStr">
         <is>
@@ -16361,9 +14728,7 @@
         </is>
       </c>
       <c r="G30" s="482" t="n"/>
-      <c r="H30" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H30" s="397" t="n"/>
       <c r="I30" s="99" t="n"/>
       <c r="J30" s="607" t="inlineStr">
         <is>
@@ -16392,7 +14757,7 @@
       <c r="Q30" s="482" t="n"/>
       <c r="R30" s="11" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15" customHeight="1" s="227">
       <c r="A31" s="33" t="n"/>
       <c r="B31" s="515" t="inlineStr">
         <is>
@@ -16400,9 +14765,7 @@
         </is>
       </c>
       <c r="C31" s="482" t="n"/>
-      <c r="D31" s="515" t="n">
-        <v>132</v>
-      </c>
+      <c r="D31" s="515" t="n"/>
       <c r="E31" s="482" t="n"/>
       <c r="F31" s="515" t="inlineStr">
         <is>
@@ -16410,9 +14773,7 @@
         </is>
       </c>
       <c r="G31" s="482" t="n"/>
-      <c r="H31" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H31" s="397" t="n"/>
       <c r="I31" s="99" t="n"/>
       <c r="J31" s="607" t="inlineStr">
         <is>
@@ -16441,7 +14802,7 @@
       <c r="Q31" s="482" t="n"/>
       <c r="R31" s="11" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15" customHeight="1" s="227">
       <c r="A32" s="33" t="n"/>
       <c r="B32" s="515" t="inlineStr">
         <is>
@@ -16449,9 +14810,7 @@
         </is>
       </c>
       <c r="C32" s="482" t="n"/>
-      <c r="D32" s="515" t="n">
-        <v>60.8</v>
-      </c>
+      <c r="D32" s="515" t="n"/>
       <c r="E32" s="482" t="n"/>
       <c r="F32" s="515" t="inlineStr">
         <is>
@@ -16459,9 +14818,7 @@
         </is>
       </c>
       <c r="G32" s="482" t="n"/>
-      <c r="H32" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H32" s="397" t="n"/>
       <c r="I32" s="99" t="n"/>
       <c r="J32" s="607" t="inlineStr">
         <is>
@@ -16490,7 +14847,7 @@
       <c r="Q32" s="482" t="n"/>
       <c r="R32" s="11" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15" customHeight="1" s="227">
       <c r="A33" s="33" t="n"/>
       <c r="B33" s="118" t="n"/>
       <c r="C33" s="52" t="n"/>
@@ -16530,7 +14887,7 @@
       <c r="Q34" s="143" t="n"/>
       <c r="R34" s="11" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15" customHeight="1" s="227">
       <c r="A35" s="33" t="n"/>
       <c r="B35" s="240" t="n"/>
       <c r="C35" s="27" t="n"/>
@@ -16550,7 +14907,7 @@
       <c r="Q35" s="143" t="n"/>
       <c r="R35" s="11" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15" customHeight="1" s="227">
       <c r="A36" s="33" t="n"/>
       <c r="B36" s="240" t="n"/>
       <c r="C36" s="27" t="n"/>
@@ -16570,7 +14927,7 @@
       <c r="Q36" s="143" t="n"/>
       <c r="R36" s="11" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15" customHeight="1" s="227">
       <c r="A37" s="33" t="n"/>
       <c r="B37" s="240" t="n"/>
       <c r="C37" s="27" t="n"/>
@@ -16674,7 +15031,7 @@
       <c r="Q42" s="362" t="n"/>
       <c r="R42" s="11" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15" customHeight="1" s="227">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="49" t="n"/>
       <c r="C43" s="637" t="n"/>
@@ -16976,7 +15333,7 @@
     <col width="9.140625" customWidth="1" style="227" min="19" max="19"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1" s="227">
       <c r="A1" s="12" t="n"/>
       <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
@@ -17168,7 +15525,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" ht="15" customHeight="1" s="227">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="421" t="inlineStr">
         <is>
@@ -17189,11 +15546,7 @@
         </is>
       </c>
       <c r="I9" s="482" t="n"/>
-      <c r="J9" s="374" t="inlineStr">
-        <is>
-          <t>METREL MI 3210</t>
-        </is>
-      </c>
+      <c r="J9" s="374" t="n"/>
       <c r="K9" s="99" t="n"/>
       <c r="L9" s="482" t="n"/>
       <c r="M9" s="374" t="inlineStr">
@@ -17202,9 +15555,7 @@
         </is>
       </c>
       <c r="N9" s="482" t="n"/>
-      <c r="O9" s="374" t="n">
-        <v>16060016</v>
-      </c>
+      <c r="O9" s="374" t="n"/>
       <c r="P9" s="99" t="n"/>
       <c r="Q9" s="482" t="n"/>
       <c r="R9" s="11" t="n"/>
@@ -17320,7 +15671,7 @@
       <c r="Q14" s="143" t="n"/>
       <c r="R14" s="11" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="15" customHeight="1" s="227">
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="345" t="inlineStr">
         <is>
@@ -17362,7 +15713,7 @@
       <c r="Q15" s="482" t="n"/>
       <c r="R15" s="11" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="15" customHeight="1" s="227">
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="515" t="inlineStr">
         <is>
@@ -17370,9 +15721,7 @@
         </is>
       </c>
       <c r="C16" s="482" t="n"/>
-      <c r="D16" s="515" t="n">
-        <v>1500</v>
-      </c>
+      <c r="D16" s="515" t="n"/>
       <c r="E16" s="482" t="n"/>
       <c r="F16" s="516" t="inlineStr">
         <is>
@@ -17380,9 +15729,7 @@
         </is>
       </c>
       <c r="G16" s="482" t="n"/>
-      <c r="H16" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H16" s="397" t="n"/>
       <c r="I16" s="99" t="n"/>
       <c r="J16" s="607" t="inlineStr">
         <is>
@@ -17411,7 +15758,7 @@
       <c r="Q16" s="482" t="n"/>
       <c r="R16" s="11" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="15" customHeight="1" s="227">
       <c r="A17" s="10" t="n"/>
       <c r="B17" s="515" t="inlineStr">
         <is>
@@ -17419,9 +15766,7 @@
         </is>
       </c>
       <c r="C17" s="482" t="n"/>
-      <c r="D17" s="515" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D17" s="515" t="n"/>
       <c r="E17" s="482" t="n"/>
       <c r="F17" s="515" t="inlineStr">
         <is>
@@ -17429,9 +15774,7 @@
         </is>
       </c>
       <c r="G17" s="482" t="n"/>
-      <c r="H17" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H17" s="397" t="n"/>
       <c r="I17" s="99" t="n"/>
       <c r="J17" s="607" t="inlineStr">
         <is>
@@ -17465,7 +15808,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="15" customHeight="1" s="227">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="515" t="inlineStr">
         <is>
@@ -17473,9 +15816,7 @@
         </is>
       </c>
       <c r="C18" s="482" t="n"/>
-      <c r="D18" s="515" t="n">
-        <v>10000</v>
-      </c>
+      <c r="D18" s="515" t="n"/>
       <c r="E18" s="482" t="n"/>
       <c r="F18" s="515" t="inlineStr">
         <is>
@@ -17483,9 +15824,7 @@
         </is>
       </c>
       <c r="G18" s="482" t="n"/>
-      <c r="H18" s="397" t="n">
-        <v>10000</v>
-      </c>
+      <c r="H18" s="397" t="n"/>
       <c r="I18" s="99" t="n"/>
       <c r="J18" s="607" t="inlineStr">
         <is>
@@ -17519,7 +15858,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15" customHeight="1" s="227">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="118" t="n"/>
       <c r="C19" s="423" t="n"/>
@@ -17537,7 +15876,7 @@
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="15" customHeight="1" s="227">
       <c r="A20" s="10" t="n"/>
       <c r="B20" s="118" t="n"/>
       <c r="C20" s="423" t="n"/>
@@ -17558,7 +15897,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="15" customHeight="1" s="227">
       <c r="A21" s="10" t="n"/>
       <c r="B21" s="118" t="n"/>
       <c r="C21" s="423" t="n"/>
@@ -17579,7 +15918,7 @@
         </is>
       </c>
     </row>
-    <row r="22">
+    <row r="22" ht="15" customHeight="1" s="227">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="118" t="n"/>
       <c r="C22" s="423" t="n"/>
@@ -17624,7 +15963,7 @@
       <c r="Q23" s="135" t="n"/>
       <c r="R23" s="11" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15" customHeight="1" s="227">
       <c r="A24" s="10" t="n"/>
       <c r="B24" s="3" t="n"/>
       <c r="C24" s="127" t="n"/>
@@ -17644,7 +15983,7 @@
       <c r="Q24" s="143" t="n"/>
       <c r="R24" s="11" t="n"/>
     </row>
-    <row r="25">
+    <row r="25" ht="15" customHeight="1" s="227">
       <c r="A25" s="10" t="n"/>
       <c r="B25" s="3" t="n"/>
       <c r="C25" s="127" t="n"/>
@@ -17664,7 +16003,7 @@
       <c r="Q25" s="143" t="n"/>
       <c r="R25" s="11" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15" customHeight="1" s="227">
       <c r="A26" s="10" t="n"/>
       <c r="B26" s="24" t="n"/>
       <c r="C26" s="25" t="n"/>
@@ -17684,7 +16023,7 @@
       <c r="Q26" s="143" t="n"/>
       <c r="R26" s="11" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15" customHeight="1" s="227">
       <c r="A27" s="10" t="n"/>
       <c r="B27" s="3" t="n"/>
       <c r="C27" s="127" t="n"/>
@@ -17704,7 +16043,7 @@
       <c r="Q27" s="143" t="n"/>
       <c r="R27" s="11" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15" customHeight="1" s="227">
       <c r="A28" s="10" t="n"/>
       <c r="B28" s="3" t="n"/>
       <c r="C28" s="127" t="n"/>
@@ -17823,7 +16162,7 @@
       <c r="Q34" s="212" t="n"/>
       <c r="R34" s="11" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15" customHeight="1" s="227">
       <c r="A35" s="33" t="n"/>
       <c r="B35" s="240" t="n"/>
       <c r="C35" s="614" t="n"/>
@@ -17839,7 +16178,7 @@
       <c r="Q35" s="143" t="n"/>
       <c r="R35" s="11" t="n"/>
     </row>
-    <row r="36">
+    <row r="36" ht="15" customHeight="1" s="227">
       <c r="A36" s="33" t="n"/>
       <c r="B36" s="240" t="n"/>
       <c r="C36" s="614" t="n"/>
@@ -17851,7 +16190,7 @@
       <c r="Q36" s="143" t="n"/>
       <c r="R36" s="11" t="n"/>
     </row>
-    <row r="37">
+    <row r="37" ht="15" customHeight="1" s="227">
       <c r="A37" s="33" t="n"/>
       <c r="B37" s="240" t="n"/>
       <c r="C37" s="614" t="n"/>
@@ -17954,7 +16293,7 @@
       <c r="Q42" s="362" t="n"/>
       <c r="R42" s="11" t="n"/>
     </row>
-    <row r="43">
+    <row r="43" ht="15" customHeight="1" s="227">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="49" t="n"/>
       <c r="C43" s="637" t="n"/>
@@ -22112,11 +20451,7 @@
         </is>
       </c>
       <c r="C11" s="482" t="n"/>
-      <c r="D11" s="422" t="inlineStr">
-        <is>
-          <t>Hilmi GÜL</t>
-        </is>
-      </c>
+      <c r="D11" s="422" t="n"/>
       <c r="E11" s="99" t="n"/>
       <c r="F11" s="99" t="n"/>
       <c r="G11" s="482" t="n"/>
@@ -22126,11 +20461,7 @@
         </is>
       </c>
       <c r="I11" s="482" t="n"/>
-      <c r="J11" s="374" t="inlineStr">
-        <is>
-          <t>STS 5000</t>
-        </is>
-      </c>
+      <c r="J11" s="374" t="n"/>
       <c r="K11" s="99" t="n"/>
       <c r="L11" s="482" t="n"/>
       <c r="M11" s="374" t="inlineStr">
@@ -22139,11 +20470,7 @@
         </is>
       </c>
       <c r="N11" s="482" t="n"/>
-      <c r="O11" s="374" t="inlineStr">
-        <is>
-          <t>19B20</t>
-        </is>
-      </c>
+      <c r="O11" s="374" t="n"/>
       <c r="P11" s="99" t="n"/>
       <c r="Q11" s="482" t="n"/>
       <c r="R11" s="11" t="n"/>
@@ -22472,9 +20799,7 @@
         <v/>
       </c>
       <c r="H24" s="482" t="n"/>
-      <c r="I24" s="370" t="n">
-        <v>40</v>
-      </c>
+      <c r="I24" s="370" t="n"/>
       <c r="J24" s="482" t="n"/>
       <c r="K24" s="370">
         <f>'ANA SAYFA'!C55</f>
@@ -22527,9 +20852,7 @@
         <v/>
       </c>
       <c r="H25" s="482" t="n"/>
-      <c r="I25" s="370" t="n">
-        <v>40</v>
-      </c>
+      <c r="I25" s="370" t="n"/>
       <c r="J25" s="482" t="n"/>
       <c r="K25" s="370">
         <f>'ANA SAYFA'!C59</f>
@@ -22574,9 +20897,7 @@
         <v/>
       </c>
       <c r="H26" s="482" t="n"/>
-      <c r="I26" s="370" t="n">
-        <v>40</v>
-      </c>
+      <c r="I26" s="370" t="n"/>
       <c r="J26" s="482" t="n"/>
       <c r="K26" s="370">
         <f>'ANA SAYFA'!C57</f>
@@ -23458,11 +21779,7 @@
         </is>
       </c>
       <c r="I11" s="482" t="n"/>
-      <c r="J11" s="374" t="inlineStr">
-        <is>
-          <t>STS 5000</t>
-        </is>
-      </c>
+      <c r="J11" s="374" t="n"/>
       <c r="K11" s="99" t="n"/>
       <c r="L11" s="482" t="n"/>
       <c r="M11" s="374" t="inlineStr">
@@ -23471,11 +21788,7 @@
         </is>
       </c>
       <c r="N11" s="482" t="n"/>
-      <c r="O11" s="374" t="inlineStr">
-        <is>
-          <t>19B20</t>
-        </is>
-      </c>
+      <c r="O11" s="374" t="n"/>
       <c r="P11" s="99" t="n"/>
       <c r="Q11" s="482" t="n"/>
       <c r="R11" s="11" t="n"/>
@@ -23800,9 +22113,7 @@
         <v/>
       </c>
       <c r="H24" s="482" t="n"/>
-      <c r="I24" s="370" t="n">
-        <v>35</v>
-      </c>
+      <c r="I24" s="370" t="n"/>
       <c r="J24" s="482" t="n"/>
       <c r="K24" s="503">
         <f>'ANA SAYFA'!G55</f>
@@ -23855,9 +22166,7 @@
         <v/>
       </c>
       <c r="H25" s="482" t="n"/>
-      <c r="I25" s="370" t="n">
-        <v>35</v>
-      </c>
+      <c r="I25" s="370" t="n"/>
       <c r="J25" s="482" t="n"/>
       <c r="K25" s="503">
         <f>'ANA SAYFA'!G57</f>
@@ -23902,9 +22211,7 @@
         <v/>
       </c>
       <c r="H26" s="482" t="n"/>
-      <c r="I26" s="370" t="n">
-        <v>35</v>
-      </c>
+      <c r="I26" s="370" t="n"/>
       <c r="J26" s="482" t="n"/>
       <c r="K26" s="503">
         <f>'ANA SAYFA'!G59</f>
@@ -24847,11 +23154,7 @@
         </is>
       </c>
       <c r="I11" s="482" t="n"/>
-      <c r="J11" s="422" t="inlineStr">
-        <is>
-          <t>METREL-MI3210</t>
-        </is>
-      </c>
+      <c r="J11" s="422" t="n"/>
       <c r="K11" s="99" t="n"/>
       <c r="L11" s="482" t="n"/>
       <c r="M11" s="374" t="inlineStr">
@@ -24860,9 +23163,7 @@
         </is>
       </c>
       <c r="N11" s="482" t="n"/>
-      <c r="O11" s="374" t="n">
-        <v>16060016</v>
-      </c>
+      <c r="O11" s="374" t="n"/>
       <c r="P11" s="99" t="n"/>
       <c r="Q11" s="482" t="n"/>
       <c r="R11" s="11" t="n"/>
@@ -25045,11 +23346,7 @@
         </is>
       </c>
       <c r="C17" s="482" t="n"/>
-      <c r="D17" s="440" t="inlineStr">
-        <is>
-          <t>45 sn</t>
-        </is>
-      </c>
+      <c r="D17" s="440" t="n"/>
       <c r="E17" s="482" t="n"/>
       <c r="F17" s="440" t="inlineStr">
         <is>
@@ -26644,11 +24941,7 @@
         </is>
       </c>
       <c r="I11" s="482" t="n"/>
-      <c r="J11" s="374" t="inlineStr">
-        <is>
-          <t>STS 5000</t>
-        </is>
-      </c>
+      <c r="J11" s="374" t="n"/>
       <c r="K11" s="99" t="n"/>
       <c r="L11" s="482" t="n"/>
       <c r="M11" s="374" t="inlineStr">
@@ -26657,11 +24950,7 @@
         </is>
       </c>
       <c r="N11" s="482" t="n"/>
-      <c r="O11" s="374" t="inlineStr">
-        <is>
-          <t>19B20</t>
-        </is>
-      </c>
+      <c r="O11" s="374" t="n"/>
       <c r="P11" s="99" t="n"/>
       <c r="Q11" s="482" t="n"/>
       <c r="R11" s="11" t="n"/>
@@ -26815,11 +25104,7 @@
     </row>
     <row r="17">
       <c r="A17" s="10" t="n"/>
-      <c r="B17" s="384" t="inlineStr">
-        <is>
-          <t>Nominal Değerler</t>
-        </is>
-      </c>
+      <c r="B17" s="384" t="n"/>
       <c r="F17" s="446" t="n"/>
       <c r="J17" s="385" t="inlineStr">
         <is>
@@ -26842,11 +25127,7 @@
     </row>
     <row r="18">
       <c r="A18" s="10" t="n"/>
-      <c r="B18" s="377" t="inlineStr">
-        <is>
-          <t>HV Kademeler</t>
-        </is>
-      </c>
+      <c r="B18" s="377" t="n"/>
       <c r="F18" s="463">
         <f>'ANA SAYFA'!O59</f>
         <v/>
@@ -26880,11 +25161,7 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" s="227">
       <c r="A19" s="10" t="n"/>
-      <c r="B19" s="377" t="inlineStr">
-        <is>
-          <t>LV Ratings</t>
-        </is>
-      </c>
+      <c r="B19" s="377" t="n"/>
       <c r="F19" s="461" t="n">
         <v>231</v>
       </c>
@@ -26920,11 +25197,7 @@
     </row>
     <row r="20" ht="15.75" customHeight="1" s="227">
       <c r="A20" s="10" t="n"/>
-      <c r="B20" s="377" t="inlineStr">
-        <is>
-          <t>Çevirme Oranı</t>
-        </is>
-      </c>
+      <c r="B20" s="377" t="n"/>
       <c r="F20" s="462">
         <f>F18/T15</f>
         <v/>
@@ -27838,7 +26111,7 @@
     <col width="3.5703125" customWidth="1" style="227" min="18" max="18"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1" s="227">
       <c r="A1" s="12" t="n"/>
       <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
@@ -27920,7 +26193,7 @@
       <c r="Q3" s="213" t="n"/>
       <c r="R3" s="11" t="n"/>
     </row>
-    <row r="4">
+    <row r="4" ht="15" customHeight="1" s="227">
       <c r="A4" s="10" t="n"/>
       <c r="B4" s="3" t="n"/>
       <c r="C4" s="127" t="n"/>
@@ -27968,7 +26241,7 @@
       <c r="Q5" s="482" t="n"/>
       <c r="R5" s="11" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1" s="227">
       <c r="A6" s="10" t="n"/>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="127" t="n"/>
@@ -28035,7 +26308,7 @@
       <c r="Q8" s="143" t="n"/>
       <c r="R8" s="11" t="n"/>
     </row>
-    <row r="9">
+    <row r="9" ht="15" customHeight="1" s="227">
       <c r="A9" s="10" t="n"/>
       <c r="B9" s="421" t="inlineStr">
         <is>
@@ -28056,11 +26329,7 @@
         </is>
       </c>
       <c r="I9" s="482" t="n"/>
-      <c r="J9" s="374" t="inlineStr">
-        <is>
-          <t>METREL-MI3123</t>
-        </is>
-      </c>
+      <c r="J9" s="374" t="n"/>
       <c r="K9" s="99" t="n"/>
       <c r="L9" s="482" t="n"/>
       <c r="M9" s="374" t="inlineStr">
@@ -28069,9 +26338,7 @@
         </is>
       </c>
       <c r="N9" s="482" t="n"/>
-      <c r="O9" s="374" t="n">
-        <v>16350177</v>
-      </c>
+      <c r="O9" s="374" t="n"/>
       <c r="P9" s="99" t="n"/>
       <c r="Q9" s="482" t="n"/>
       <c r="R9" s="11" t="n"/>
@@ -28184,7 +26451,7 @@
       <c r="Q14" s="143" t="n"/>
       <c r="R14" s="11" t="n"/>
     </row>
-    <row r="15">
+    <row r="15" ht="15" customHeight="1" s="227">
       <c r="A15" s="10" t="n"/>
       <c r="B15" s="345" t="n"/>
       <c r="C15" s="99" t="n"/>
@@ -28208,7 +26475,7 @@
       <c r="Q15" s="482" t="n"/>
       <c r="R15" s="11" t="n"/>
     </row>
-    <row r="16">
+    <row r="16" ht="15" customHeight="1" s="227">
       <c r="A16" s="10" t="n"/>
       <c r="B16" s="515" t="inlineStr">
         <is>
@@ -28256,7 +26523,7 @@
       <c r="Q16" s="482" t="n"/>
       <c r="R16" s="11" t="n"/>
     </row>
-    <row r="17">
+    <row r="17" ht="15" customHeight="1" s="227">
       <c r="A17" s="10" t="n"/>
       <c r="B17" s="518" t="n"/>
       <c r="C17" s="519" t="n"/>
@@ -28276,7 +26543,7 @@
       <c r="Q17" s="428" t="n"/>
       <c r="R17" s="11" t="n"/>
     </row>
-    <row r="18">
+    <row r="18" ht="15" customHeight="1" s="227">
       <c r="A18" s="10" t="n"/>
       <c r="B18" s="521" t="n"/>
       <c r="C18" s="45" t="n"/>
@@ -28306,7 +26573,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="15" customHeight="1" s="227">
       <c r="A19" s="10" t="n"/>
       <c r="B19" s="521" t="n"/>
       <c r="C19" s="45" t="n"/>
@@ -28326,7 +26593,7 @@
       <c r="Q19" s="522" t="n"/>
       <c r="R19" s="11" t="n"/>
     </row>
-    <row r="20">
+    <row r="20" ht="15" customHeight="1" s="227">
       <c r="A20" s="10" t="n"/>
       <c r="B20" s="521" t="n"/>
       <c r="C20" s="45" t="n"/>
@@ -28346,7 +26613,7 @@
       <c r="Q20" s="522" t="n"/>
       <c r="R20" s="11" t="n"/>
     </row>
-    <row r="21">
+    <row r="21" ht="15" customHeight="1" s="227">
       <c r="A21" s="10" t="n"/>
       <c r="B21" s="521" t="n"/>
       <c r="C21" s="45" t="n"/>
@@ -28366,7 +26633,7 @@
       <c r="Q21" s="522" t="n"/>
       <c r="R21" s="11" t="n"/>
     </row>
-    <row r="22">
+    <row r="22" ht="15" customHeight="1" s="227">
       <c r="A22" s="10" t="n"/>
       <c r="B22" s="521" t="n"/>
       <c r="C22" s="45" t="n"/>
@@ -28746,7 +27013,7 @@
         </is>
       </c>
     </row>
-    <row r="32">
+    <row r="32" ht="15" customHeight="1" s="227">
       <c r="A32" s="10" t="n"/>
       <c r="B32" s="3" t="n"/>
       <c r="C32" s="127" t="n"/>
@@ -28816,7 +27083,7 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="15" customHeight="1" s="227">
       <c r="A35" s="10" t="n"/>
       <c r="B35" s="3" t="n"/>
       <c r="C35" s="127" t="n"/>
@@ -29324,7 +27591,7 @@
     <col width="9.140625" customWidth="1" style="227" min="28" max="28"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1" s="227">
       <c r="A1" s="12" t="n"/>
       <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
@@ -29459,7 +27726,7 @@
       <c r="R5" s="11" t="n"/>
       <c r="V5" s="446" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1" s="227">
       <c r="A6" s="10" t="n"/>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="127" t="n"/>
@@ -29491,7 +27758,7 @@
       </c>
       <c r="Y6" s="211" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1" s="227">
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="374" t="inlineStr">
         <is>
@@ -29672,11 +27939,7 @@
         </is>
       </c>
       <c r="I11" s="482" t="n"/>
-      <c r="J11" s="374" t="inlineStr">
-        <is>
-          <t>STS 5000</t>
-        </is>
-      </c>
+      <c r="J11" s="374" t="n"/>
       <c r="K11" s="99" t="n"/>
       <c r="L11" s="482" t="n"/>
       <c r="M11" s="374" t="inlineStr">
@@ -29685,11 +27948,7 @@
         </is>
       </c>
       <c r="N11" s="482" t="n"/>
-      <c r="O11" s="374" t="inlineStr">
-        <is>
-          <t>19B20</t>
-        </is>
-      </c>
+      <c r="O11" s="374" t="n"/>
       <c r="P11" s="99" t="n"/>
       <c r="Q11" s="482" t="n"/>
       <c r="R11" s="11" t="n"/>
@@ -29939,9 +28198,7 @@
         <v>10000</v>
       </c>
       <c r="O17" s="482" t="n"/>
-      <c r="P17" s="445" t="n">
-        <v>50</v>
-      </c>
+      <c r="P17" s="445" t="n"/>
       <c r="Q17" s="482" t="n"/>
       <c r="R17" s="11" t="n"/>
       <c r="V17" s="504" t="n">
@@ -30176,7 +28433,7 @@
       <c r="Q22" s="482" t="n"/>
       <c r="R22" s="11" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15" customHeight="1" s="227">
       <c r="A23" s="10" t="n"/>
       <c r="B23" s="539" t="n"/>
       <c r="C23" s="398" t="n">
@@ -30213,7 +28470,7 @@
       <c r="Q23" s="482" t="n"/>
       <c r="R23" s="11" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15" customHeight="1" s="227">
       <c r="A24" s="33" t="n"/>
       <c r="B24" s="539" t="n"/>
       <c r="C24" s="127" t="n"/>
@@ -30257,7 +28514,7 @@
       <c r="Q25" s="482" t="n"/>
       <c r="R25" s="11" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15" customHeight="1" s="227">
       <c r="A26" s="33" t="n"/>
       <c r="B26" s="539" t="n"/>
       <c r="C26" s="398" t="inlineStr">
@@ -30309,7 +28566,7 @@
       <c r="Q26" s="482" t="n"/>
       <c r="R26" s="11" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15" customHeight="1" s="227">
       <c r="A27" s="10" t="n"/>
       <c r="B27" s="539" t="n"/>
       <c r="C27" s="398" t="n">
@@ -30346,7 +28603,7 @@
       <c r="Q27" s="482" t="n"/>
       <c r="R27" s="11" t="n"/>
     </row>
-    <row r="28">
+    <row r="28" ht="15" customHeight="1" s="227">
       <c r="A28" s="10" t="n"/>
       <c r="B28" s="539" t="n"/>
       <c r="C28" s="127" t="n"/>
@@ -30390,7 +28647,7 @@
       <c r="Q29" s="482" t="n"/>
       <c r="R29" s="11" t="n"/>
     </row>
-    <row r="30">
+    <row r="30" ht="15" customHeight="1" s="227">
       <c r="A30" s="10" t="n"/>
       <c r="B30" s="539" t="n"/>
       <c r="C30" s="398" t="inlineStr">
@@ -30442,7 +28699,7 @@
       <c r="Q30" s="482" t="n"/>
       <c r="R30" s="11" t="n"/>
     </row>
-    <row r="31">
+    <row r="31" ht="15" customHeight="1" s="227">
       <c r="A31" s="10" t="n"/>
       <c r="B31" s="541" t="n"/>
       <c r="C31" s="398" t="n">
@@ -30480,7 +28737,7 @@
       <c r="Q31" s="482" t="n"/>
       <c r="R31" s="11" t="n"/>
     </row>
-    <row r="32">
+    <row r="32" ht="15" customHeight="1" s="227">
       <c r="A32" s="10" t="n"/>
       <c r="B32" s="543" t="n"/>
       <c r="C32" s="127" t="n"/>
@@ -30500,7 +28757,7 @@
       <c r="Q32" s="143" t="n"/>
       <c r="R32" s="11" t="n"/>
     </row>
-    <row r="33">
+    <row r="33" ht="15" customHeight="1" s="227">
       <c r="A33" s="10" t="n"/>
       <c r="B33" s="544" t="inlineStr">
         <is>
@@ -30517,7 +28774,7 @@
       <c r="R34" s="11" t="n"/>
       <c r="V34" s="127" t="n"/>
     </row>
-    <row r="35">
+    <row r="35" ht="15" customHeight="1" s="227">
       <c r="A35" s="10" t="n"/>
       <c r="B35" s="62" t="n"/>
       <c r="Q35" s="212" t="n"/>
@@ -30571,7 +28828,7 @@
       <c r="Q37" s="211" t="n"/>
       <c r="R37" s="11" t="n"/>
     </row>
-    <row r="38">
+    <row r="38" ht="15" customHeight="1" s="227">
       <c r="A38" s="10" t="n"/>
       <c r="B38" s="49" t="n"/>
       <c r="C38" s="50" t="n"/>
@@ -30591,7 +28848,7 @@
       <c r="Q38" s="213" t="n"/>
       <c r="R38" s="11" t="n"/>
     </row>
-    <row r="39">
+    <row r="39" ht="15" customHeight="1" s="227">
       <c r="A39" s="10" t="n"/>
       <c r="B39" s="545" t="inlineStr">
         <is>
@@ -30858,8 +29115,8 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J11:L11"/>
     <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="J11:L11"/>
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K17:M17"/>
@@ -30877,8 +29134,8 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="J23:K23"/>
+    <mergeCell ref="B16:B19"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B16:B19"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="V3:AC3"/>
@@ -31016,7 +29273,7 @@
     <col width="9.140625" customWidth="1" style="227" min="28" max="28"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="15" customHeight="1" s="227">
       <c r="A1" s="12" t="n"/>
       <c r="B1" s="13" t="n"/>
       <c r="C1" s="13" t="n"/>
@@ -31151,7 +29408,7 @@
       <c r="R5" s="11" t="n"/>
       <c r="V5" s="446" t="n"/>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1" s="227">
       <c r="A6" s="10" t="n"/>
       <c r="B6" s="3" t="n"/>
       <c r="C6" s="127" t="n"/>
@@ -31183,7 +29440,7 @@
       </c>
       <c r="Y6" s="211" t="n"/>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1" s="227">
       <c r="A7" s="10" t="n"/>
       <c r="B7" s="374" t="inlineStr">
         <is>
@@ -31364,11 +29621,7 @@
         </is>
       </c>
       <c r="I11" s="482" t="n"/>
-      <c r="J11" s="374" t="inlineStr">
-        <is>
-          <t>STS 5000</t>
-        </is>
-      </c>
+      <c r="J11" s="374" t="n"/>
       <c r="K11" s="99" t="n"/>
       <c r="L11" s="482" t="n"/>
       <c r="M11" s="374" t="inlineStr">
@@ -31377,11 +29630,7 @@
         </is>
       </c>
       <c r="N11" s="482" t="n"/>
-      <c r="O11" s="374" t="inlineStr">
-        <is>
-          <t>19B20</t>
-        </is>
-      </c>
+      <c r="O11" s="374" t="n"/>
       <c r="P11" s="99" t="n"/>
       <c r="Q11" s="482" t="n"/>
       <c r="R11" s="11" t="n"/>
@@ -31631,9 +29880,7 @@
         <v>10000</v>
       </c>
       <c r="O17" s="482" t="n"/>
-      <c r="P17" s="445" t="n">
-        <v>50</v>
-      </c>
+      <c r="P17" s="445" t="n"/>
       <c r="Q17" s="482" t="n"/>
       <c r="R17" s="11" t="n"/>
       <c r="V17" s="504" t="n">
@@ -31868,7 +30115,7 @@
       <c r="Q22" s="482" t="n"/>
       <c r="R22" s="11" t="n"/>
     </row>
-    <row r="23">
+    <row r="23" ht="15" customHeight="1" s="227">
       <c r="A23" s="10" t="n"/>
       <c r="B23" s="539" t="n"/>
       <c r="C23" s="398" t="n">
@@ -31905,7 +30152,7 @@
       <c r="Q23" s="482" t="n"/>
       <c r="R23" s="11" t="n"/>
     </row>
-    <row r="24">
+    <row r="24" ht="15" customHeight="1" s="227">
       <c r="A24" s="33" t="n"/>
       <c r="B24" s="539" t="n"/>
       <c r="C24" s="127" t="n"/>
@@ -31949,7 +30196,7 @@
       <c r="Q25" s="482" t="n"/>
       <c r="R25" s="11" t="n"/>
     </row>
-    <row r="26">
+    <row r="26" ht="15" customHeight="1" s="227">
       <c r="A26" s="33" t="n"/>
       <c r="B26" s="539" t="n"/>
       <c r="C26" s="398" t="inlineStr">
@@ -32001,7 +30248,7 @@
       <c r="Q26" s="482" t="n"/>
       <c r="R26" s="11" t="n"/>
     </row>
-    <row r="27">
+    <row r="27" ht="15" customHeight="1" s="227">
       <c r="A27" s="10" t="n"/>
       <c r="B27" s="539" t="n"/>
       <c r="C27" s="398" t="n">
@@ -32695,8 +30942,8 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J11:L11"/>
     <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="J11:L11"/>
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K17:M17"/>
@@ -32714,8 +30961,8 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="J23:K23"/>
+    <mergeCell ref="B16:B19"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B16:B19"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="V3:AC3"/>

--- a/backend/templates/hybrid/hermetik_hybrid.xlsx
+++ b/backend/templates/hybrid/hermetik_hybrid.xlsx
@@ -9778,7 +9778,8 @@
     <mergeCell ref="O17:S17"/>
     <mergeCell ref="O11:S11"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -10779,8 +10780,8 @@
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="J40:Q40"/>
     <mergeCell ref="B5:Q5"/>
-    <mergeCell ref="J40:Q40"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="D37:Q38"/>
     <mergeCell ref="K3:Q3"/>
@@ -10823,7 +10824,8 @@
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="K18:L18"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -12147,8 +12149,8 @@
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="F16:I16"/>
     <mergeCell ref="F25:I25"/>
+    <mergeCell ref="N39:O39"/>
     <mergeCell ref="B8:I8"/>
-    <mergeCell ref="N39:O39"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="P39:Q39"/>
     <mergeCell ref="J28:M28"/>
@@ -12264,7 +12266,8 @@
     <mergeCell ref="K2:Q2"/>
     <mergeCell ref="N36:O36"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -13795,8 +13798,8 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="B28:E28"/>
+    <mergeCell ref="I27:I28"/>
     <mergeCell ref="W38:AJ38"/>
-    <mergeCell ref="I27:I28"/>
     <mergeCell ref="J23:Q23"/>
     <mergeCell ref="W28:AD28"/>
     <mergeCell ref="N19:Q19"/>
@@ -13817,7 +13820,8 @@
     <mergeCell ref="W42:AJ42"/>
     <mergeCell ref="K2:Q2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -15313,7 +15317,8 @@
     <mergeCell ref="O30:Q30"/>
     <mergeCell ref="B13:Q13"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -16561,7 +16566,8 @@
     <mergeCell ref="L36:M36"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -27560,7 +27566,8 @@
     <mergeCell ref="H25:J25"/>
     <mergeCell ref="H26:I26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -29115,8 +29122,8 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:Q22"/>
     <mergeCell ref="J11:L11"/>
-    <mergeCell ref="P22:Q22"/>
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K17:M17"/>
@@ -29134,8 +29141,8 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D26:E26"/>
     <mergeCell ref="B16:B19"/>
-    <mergeCell ref="D26:E26"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="V3:AC3"/>
@@ -29242,7 +29249,8 @@
     <mergeCell ref="V18:W18"/>
     <mergeCell ref="H26:I26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
@@ -30942,8 +30950,8 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="P22:Q22"/>
     <mergeCell ref="J11:L11"/>
-    <mergeCell ref="P22:Q22"/>
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K17:M17"/>
@@ -30961,8 +30969,8 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="J23:K23"/>
+    <mergeCell ref="D26:E26"/>
     <mergeCell ref="B16:B19"/>
-    <mergeCell ref="D26:E26"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="V3:AC3"/>
@@ -31069,7 +31077,8 @@
     <mergeCell ref="V18:W18"/>
     <mergeCell ref="H26:I26"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.1968503937007874" right="0.1968503937007874" top="0.3543307086614173" bottom="0.3543307086614173" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/backend/templates/hybrid/hermetik_hybrid.xlsx
+++ b/backend/templates/hybrid/hermetik_hybrid.xlsx
@@ -10780,8 +10780,8 @@
     <mergeCell ref="F19:G19"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="J40:Q40"/>
-    <mergeCell ref="B5:Q5"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="D37:Q38"/>
     <mergeCell ref="K3:Q3"/>
@@ -12149,8 +12149,8 @@
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="F16:I16"/>
     <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B8:I8"/>
     <mergeCell ref="N39:O39"/>
-    <mergeCell ref="B8:I8"/>
     <mergeCell ref="J19:M19"/>
     <mergeCell ref="P39:Q39"/>
     <mergeCell ref="J28:M28"/>
@@ -13798,8 +13798,8 @@
     <mergeCell ref="B19:E19"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="B28:E28"/>
+    <mergeCell ref="W38:AJ38"/>
     <mergeCell ref="I27:I28"/>
-    <mergeCell ref="W38:AJ38"/>
     <mergeCell ref="J23:Q23"/>
     <mergeCell ref="W28:AD28"/>
     <mergeCell ref="N19:Q19"/>
@@ -29122,8 +29122,8 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J11:L11"/>
     <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="J11:L11"/>
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K17:M17"/>
@@ -29141,8 +29141,8 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="J23:K23"/>
+    <mergeCell ref="B16:B19"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B16:B19"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="V3:AC3"/>
@@ -30950,8 +30950,8 @@
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="N22:O22"/>
+    <mergeCell ref="J11:L11"/>
     <mergeCell ref="P22:Q22"/>
-    <mergeCell ref="J11:L11"/>
     <mergeCell ref="V20:W20"/>
     <mergeCell ref="H19:J19"/>
     <mergeCell ref="K17:M17"/>
@@ -30969,8 +30969,8 @@
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="H23:I23"/>
     <mergeCell ref="J23:K23"/>
+    <mergeCell ref="B16:B19"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="B16:B19"/>
     <mergeCell ref="N26:O26"/>
     <mergeCell ref="P26:Q26"/>
     <mergeCell ref="V3:AC3"/>

--- a/backend/templates/hybrid/hermetik_hybrid.xlsx
+++ b/backend/templates/hybrid/hermetik_hybrid.xlsx
@@ -2910,7 +2910,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3063,7 +3063,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3108,7 +3108,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3348,7 +3348,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3501,7 +3501,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3546,7 +3546,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3626,7 +3626,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3695,7 +3695,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3787,7 +3787,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3905,7 +3905,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3988,7 +3988,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4057,7 +4057,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4149,7 +4149,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4267,7 +4267,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4357,7 +4357,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4430,7 +4430,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4522,7 +4522,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4640,7 +4640,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4723,7 +4723,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4820,7 +4820,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4932,7 +4932,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -4994,7 +4994,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5033,7 +5033,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -6664,25 +6664,11 @@
     <row r="30" s="227"/>
     <row r="31"/>
     <row r="32" ht="11.25" customHeight="1" s="227"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40" s="227"/>
     <row r="41" s="227"/>
     <row r="42" s="227"/>
-    <row r="43"/>
     <row r="44" s="227"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48" ht="7.5" customHeight="1" s="227"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="481" t="n"/>
       <c r="B52" s="99" t="n"/>
@@ -26490,7 +26476,7 @@
       </c>
       <c r="C16" s="482" t="n"/>
       <c r="D16" s="515" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="482" t="n"/>
       <c r="F16" s="516" t="inlineStr">
@@ -26747,7 +26733,7 @@
       </c>
       <c r="E26" s="99" t="n"/>
       <c r="F26" s="525" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G26" s="526" t="inlineStr">
         <is>
@@ -26804,7 +26790,7 @@
       </c>
       <c r="E27" s="99" t="n"/>
       <c r="F27" s="525" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G27" s="526" t="inlineStr">
         <is>
@@ -26861,7 +26847,7 @@
       </c>
       <c r="E28" s="99" t="n"/>
       <c r="F28" s="525" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G28" s="526" t="inlineStr">
         <is>
@@ -26918,7 +26904,7 @@
       </c>
       <c r="E29" s="99" t="n"/>
       <c r="F29" s="525" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G29" s="526" t="inlineStr">
         <is>

--- a/backend/templates/hybrid/hermetik_hybrid.xlsx
+++ b/backend/templates/hybrid/hermetik_hybrid.xlsx
@@ -2910,7 +2910,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3063,7 +3063,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3108,7 +3108,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3348,7 +3348,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3501,7 +3501,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3546,7 +3546,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3626,7 +3626,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3695,7 +3695,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3787,7 +3787,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3905,7 +3905,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3988,7 +3988,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4057,7 +4057,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4149,7 +4149,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4267,7 +4267,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4357,7 +4357,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4430,7 +4430,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4522,7 +4522,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4640,7 +4640,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4723,7 +4723,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4820,7 +4820,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t>None</a:t>
+                  <a:t/>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4932,7 +4932,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -4994,7 +4994,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t>None</a:t>
+              <a:t/>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5033,7 +5033,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t>None</a:t>
+            <a:t/>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -6664,11 +6664,25 @@
     <row r="30" s="227"/>
     <row r="31"/>
     <row r="32" ht="11.25" customHeight="1" s="227"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
     <row r="40" s="227"/>
     <row r="41" s="227"/>
     <row r="42" s="227"/>
+    <row r="43"/>
     <row r="44" s="227"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
     <row r="48" ht="7.5" customHeight="1" s="227"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
     <row r="52">
       <c r="A52" s="481" t="n"/>
       <c r="B52" s="99" t="n"/>

--- a/backend/templates/hybrid/hermetik_hybrid.xlsx
+++ b/backend/templates/hybrid/hermetik_hybrid.xlsx
@@ -2910,7 +2910,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3063,7 +3063,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3108,7 +3108,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3348,7 +3348,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3501,7 +3501,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -3546,7 +3546,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3626,7 +3626,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3695,7 +3695,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3787,7 +3787,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -3905,7 +3905,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -3988,7 +3988,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4057,7 +4057,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4149,7 +4149,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4267,7 +4267,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4357,7 +4357,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4430,7 +4430,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4522,7 +4522,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4640,7 +4640,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4723,7 +4723,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -4820,7 +4820,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
                 <a:endParaRPr lang="tr-TR"/>
               </a:p>
@@ -4932,7 +4932,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -4994,7 +4994,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
             <a:endParaRPr lang="tr-TR"/>
           </a:p>
@@ -5033,7 +5033,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
           <a:endParaRPr lang="tr-TR"/>
         </a:p>
@@ -6664,25 +6664,11 @@
     <row r="30" s="227"/>
     <row r="31"/>
     <row r="32" ht="11.25" customHeight="1" s="227"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
     <row r="40" s="227"/>
     <row r="41" s="227"/>
     <row r="42" s="227"/>
-    <row r="43"/>
     <row r="44" s="227"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
     <row r="48" ht="7.5" customHeight="1" s="227"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
     <row r="52">
       <c r="A52" s="481" t="n"/>
       <c r="B52" s="99" t="n"/>
@@ -18496,29 +18482,10 @@
     <row r="43" ht="3" customHeight="1" s="227">
       <c r="A43" s="10" t="n"/>
       <c r="B43" s="485" t="n"/>
-      <c r="C43" s="47" t="n"/>
-      <c r="D43" s="47" t="n"/>
-      <c r="E43" s="47" t="n"/>
-      <c r="F43" s="47" t="n"/>
-      <c r="G43" s="47" t="n"/>
-      <c r="H43" s="47" t="n"/>
-      <c r="I43" s="47" t="n"/>
-      <c r="J43" s="47" t="n"/>
-      <c r="K43" s="47" t="n"/>
-      <c r="L43" s="47" t="n"/>
-      <c r="M43" s="47" t="n"/>
-      <c r="N43" s="47" t="n"/>
-      <c r="O43" s="47" t="n"/>
-      <c r="P43" s="47" t="n"/>
-      <c r="Q43" s="47" t="n"/>
-      <c r="R43" s="47" t="n"/>
-      <c r="S43" s="211" t="n"/>
       <c r="T43" s="11" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="227">
       <c r="A44" s="10" t="n"/>
-      <c r="B44" s="62" t="n"/>
-      <c r="S44" s="212" t="n"/>
       <c r="T44" s="11" t="n"/>
       <c r="V44" s="485" t="inlineStr">
         <is>
@@ -18549,8 +18516,6 @@
     </row>
     <row r="45" ht="3" customHeight="1" s="227">
       <c r="A45" s="10" t="n"/>
-      <c r="B45" s="62" t="n"/>
-      <c r="S45" s="212" t="n"/>
       <c r="T45" s="11" t="n"/>
       <c r="V45" s="3" t="n"/>
       <c r="W45" s="127" t="n"/>
@@ -18573,8 +18538,6 @@
     </row>
     <row r="46">
       <c r="A46" s="10" t="n"/>
-      <c r="B46" s="62" t="n"/>
-      <c r="S46" s="212" t="n"/>
       <c r="T46" s="11" t="n"/>
       <c r="V46" s="489" t="inlineStr">
         <is>
@@ -18621,8 +18584,6 @@
     </row>
     <row r="47" ht="3" customHeight="1" s="227">
       <c r="A47" s="10" t="n"/>
-      <c r="B47" s="62" t="n"/>
-      <c r="S47" s="212" t="n"/>
       <c r="T47" s="11" t="n"/>
       <c r="V47" s="3" t="n"/>
       <c r="W47" s="127" t="n"/>
@@ -18645,8 +18606,6 @@
     </row>
     <row r="48">
       <c r="A48" s="10" t="n"/>
-      <c r="B48" s="62" t="n"/>
-      <c r="S48" s="212" t="n"/>
       <c r="T48" s="11" t="n"/>
       <c r="V48" s="490">
         <f>V57/1.0525889</f>
@@ -18687,8 +18646,6 @@
     </row>
     <row r="49" ht="3" customHeight="1" s="227">
       <c r="A49" s="10" t="n"/>
-      <c r="B49" s="62" t="n"/>
-      <c r="S49" s="212" t="n"/>
       <c r="T49" s="11" t="n"/>
       <c r="V49" s="42" t="n"/>
       <c r="W49" s="43" t="n"/>
@@ -18711,8 +18668,6 @@
     </row>
     <row r="50">
       <c r="A50" s="10" t="n"/>
-      <c r="B50" s="62" t="n"/>
-      <c r="S50" s="212" t="n"/>
       <c r="T50" s="11" t="n"/>
       <c r="V50" s="328" t="inlineStr">
         <is>
@@ -18759,24 +18714,6 @@
     </row>
     <row r="51" ht="3" customHeight="1" s="227">
       <c r="A51" s="10" t="n"/>
-      <c r="B51" s="49" t="n"/>
-      <c r="C51" s="50" t="n"/>
-      <c r="D51" s="50" t="n"/>
-      <c r="E51" s="50" t="n"/>
-      <c r="F51" s="50" t="n"/>
-      <c r="G51" s="50" t="n"/>
-      <c r="H51" s="50" t="n"/>
-      <c r="I51" s="50" t="n"/>
-      <c r="J51" s="50" t="n"/>
-      <c r="K51" s="50" t="n"/>
-      <c r="L51" s="50" t="n"/>
-      <c r="M51" s="50" t="n"/>
-      <c r="N51" s="50" t="n"/>
-      <c r="O51" s="50" t="n"/>
-      <c r="P51" s="50" t="n"/>
-      <c r="Q51" s="50" t="n"/>
-      <c r="R51" s="50" t="n"/>
-      <c r="S51" s="213" t="n"/>
       <c r="T51" s="11" t="n"/>
     </row>
     <row r="52" ht="3" customHeight="1" s="227">
@@ -20011,7 +19948,7 @@
       <c r="T83" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="161">
+  <mergeCells count="160">
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="F68:G68"/>
     <mergeCell ref="AL57:AN57"/>
@@ -20023,7 +19960,6 @@
     <mergeCell ref="L68:M68"/>
     <mergeCell ref="K5:S6"/>
     <mergeCell ref="V66:X66"/>
-    <mergeCell ref="B43:S51"/>
     <mergeCell ref="K17:M17"/>
     <mergeCell ref="I66:J66"/>
     <mergeCell ref="K33:N33"/>
